--- a/data/trans_orig/IP1006-Estudios-trans_orig.xlsx
+++ b/data/trans_orig/IP1006-Estudios-trans_orig.xlsx
@@ -737,7 +737,7 @@
       </c>
       <c r="F4" s="2" t="inlineStr">
         <is>
-          <t>4314</t>
+          <t>4673</t>
         </is>
       </c>
       <c r="G4" s="2" t="inlineStr">
@@ -752,7 +752,7 @@
       </c>
       <c r="I4" s="2" t="inlineStr">
         <is>
-          <t>4,75%</t>
+          <t>5,14%</t>
         </is>
       </c>
       <c r="J4" s="2" t="inlineStr">
@@ -807,7 +807,7 @@
       </c>
       <c r="T4" s="2" t="inlineStr">
         <is>
-          <t>4624</t>
+          <t>4122</t>
         </is>
       </c>
       <c r="U4" s="2" t="inlineStr">
@@ -822,7 +822,7 @@
       </c>
       <c r="W4" s="2" t="inlineStr">
         <is>
-          <t>2,6%</t>
+          <t>2,32%</t>
         </is>
       </c>
     </row>
@@ -845,7 +845,7 @@
       </c>
       <c r="E5" s="2" t="inlineStr">
         <is>
-          <t>86553</t>
+          <t>86194</t>
         </is>
       </c>
       <c r="F5" s="2" t="inlineStr">
@@ -860,7 +860,7 @@
       </c>
       <c r="H5" s="2" t="inlineStr">
         <is>
-          <t>95,25%</t>
+          <t>94,86%</t>
         </is>
       </c>
       <c r="I5" s="2" t="inlineStr">
@@ -915,7 +915,7 @@
       </c>
       <c r="S5" s="2" t="inlineStr">
         <is>
-          <t>173088</t>
+          <t>173590</t>
         </is>
       </c>
       <c r="T5" s="2" t="inlineStr">
@@ -930,7 +930,7 @@
       </c>
       <c r="V5" s="2" t="inlineStr">
         <is>
-          <t>97,4%</t>
+          <t>97,68%</t>
         </is>
       </c>
       <c r="W5" s="2" t="inlineStr">
@@ -1080,7 +1080,7 @@
       </c>
       <c r="F7" s="2" t="inlineStr">
         <is>
-          <t>4491</t>
+          <t>3336</t>
         </is>
       </c>
       <c r="G7" s="2" t="inlineStr">
@@ -1095,7 +1095,7 @@
       </c>
       <c r="I7" s="2" t="inlineStr">
         <is>
-          <t>1,08%</t>
+          <t>0,8%</t>
         </is>
       </c>
       <c r="J7" s="2" t="inlineStr">
@@ -1110,12 +1110,12 @@
       </c>
       <c r="L7" s="2" t="inlineStr">
         <is>
-          <t>409</t>
+          <t>0</t>
         </is>
       </c>
       <c r="M7" s="2" t="inlineStr">
         <is>
-          <t>5609</t>
+          <t>5611</t>
         </is>
       </c>
       <c r="N7" s="2" t="inlineStr">
@@ -1125,7 +1125,7 @@
       </c>
       <c r="O7" s="2" t="inlineStr">
         <is>
-          <t>0,09%</t>
+          <t>0,0%</t>
         </is>
       </c>
       <c r="P7" s="2" t="inlineStr">
@@ -1145,12 +1145,12 @@
       </c>
       <c r="S7" s="2" t="inlineStr">
         <is>
-          <t>694</t>
+          <t>696</t>
         </is>
       </c>
       <c r="T7" s="2" t="inlineStr">
         <is>
-          <t>6926</t>
+          <t>6239</t>
         </is>
       </c>
       <c r="U7" s="2" t="inlineStr">
@@ -1165,7 +1165,7 @@
       </c>
       <c r="W7" s="2" t="inlineStr">
         <is>
-          <t>0,78%</t>
+          <t>0,7%</t>
         </is>
       </c>
     </row>
@@ -1188,7 +1188,7 @@
       </c>
       <c r="E8" s="2" t="inlineStr">
         <is>
-          <t>411596</t>
+          <t>412751</t>
         </is>
       </c>
       <c r="F8" s="2" t="inlineStr">
@@ -1203,7 +1203,7 @@
       </c>
       <c r="H8" s="2" t="inlineStr">
         <is>
-          <t>98,92%</t>
+          <t>99,2%</t>
         </is>
       </c>
       <c r="I8" s="2" t="inlineStr">
@@ -1223,12 +1223,12 @@
       </c>
       <c r="L8" s="2" t="inlineStr">
         <is>
-          <t>471382</t>
+          <t>471380</t>
         </is>
       </c>
       <c r="M8" s="2" t="inlineStr">
         <is>
-          <t>476582</t>
+          <t>476991</t>
         </is>
       </c>
       <c r="N8" s="2" t="inlineStr">
@@ -1243,7 +1243,7 @@
       </c>
       <c r="P8" s="2" t="inlineStr">
         <is>
-          <t>99,91%</t>
+          <t>100,0%</t>
         </is>
       </c>
       <c r="Q8" s="2" t="inlineStr">
@@ -1258,12 +1258,12 @@
       </c>
       <c r="S8" s="2" t="inlineStr">
         <is>
-          <t>886152</t>
+          <t>886839</t>
         </is>
       </c>
       <c r="T8" s="2" t="inlineStr">
         <is>
-          <t>892384</t>
+          <t>892382</t>
         </is>
       </c>
       <c r="U8" s="2" t="inlineStr">
@@ -1273,7 +1273,7 @@
       </c>
       <c r="V8" s="2" t="inlineStr">
         <is>
-          <t>99,22%</t>
+          <t>99,3%</t>
         </is>
       </c>
       <c r="W8" s="2" t="inlineStr">
@@ -1423,7 +1423,7 @@
       </c>
       <c r="F10" s="2" t="inlineStr">
         <is>
-          <t>2645</t>
+          <t>2643</t>
         </is>
       </c>
       <c r="G10" s="2" t="inlineStr">
@@ -1493,7 +1493,7 @@
       </c>
       <c r="T10" s="2" t="inlineStr">
         <is>
-          <t>3140</t>
+          <t>2120</t>
         </is>
       </c>
       <c r="U10" s="2" t="inlineStr">
@@ -1508,7 +1508,7 @@
       </c>
       <c r="W10" s="2" t="inlineStr">
         <is>
-          <t>0,95%</t>
+          <t>0,64%</t>
         </is>
       </c>
     </row>
@@ -1531,7 +1531,7 @@
       </c>
       <c r="E11" s="2" t="inlineStr">
         <is>
-          <t>171421</t>
+          <t>171423</t>
         </is>
       </c>
       <c r="F11" s="2" t="inlineStr">
@@ -1601,7 +1601,7 @@
       </c>
       <c r="S11" s="2" t="inlineStr">
         <is>
-          <t>329065</t>
+          <t>330085</t>
         </is>
       </c>
       <c r="T11" s="2" t="inlineStr">
@@ -1616,7 +1616,7 @@
       </c>
       <c r="V11" s="2" t="inlineStr">
         <is>
-          <t>99,05%</t>
+          <t>99,36%</t>
         </is>
       </c>
       <c r="W11" s="2" t="inlineStr">
@@ -1761,12 +1761,12 @@
       </c>
       <c r="E13" s="2" t="inlineStr">
         <is>
-          <t>661</t>
+          <t>642</t>
         </is>
       </c>
       <c r="F13" s="2" t="inlineStr">
         <is>
-          <t>5946</t>
+          <t>5675</t>
         </is>
       </c>
       <c r="G13" s="2" t="inlineStr">
@@ -1776,12 +1776,12 @@
       </c>
       <c r="H13" s="2" t="inlineStr">
         <is>
-          <t>0,1%</t>
+          <t>0,09%</t>
         </is>
       </c>
       <c r="I13" s="2" t="inlineStr">
         <is>
-          <t>0,87%</t>
+          <t>0,83%</t>
         </is>
       </c>
       <c r="J13" s="2" t="inlineStr">
@@ -1796,12 +1796,12 @@
       </c>
       <c r="L13" s="2" t="inlineStr">
         <is>
-          <t>685</t>
+          <t>686</t>
         </is>
       </c>
       <c r="M13" s="2" t="inlineStr">
         <is>
-          <t>5664</t>
+          <t>6321</t>
         </is>
       </c>
       <c r="N13" s="2" t="inlineStr">
@@ -1816,7 +1816,7 @@
       </c>
       <c r="P13" s="2" t="inlineStr">
         <is>
-          <t>0,78%</t>
+          <t>0,88%</t>
         </is>
       </c>
       <c r="Q13" s="2" t="inlineStr">
@@ -1831,12 +1831,12 @@
       </c>
       <c r="S13" s="2" t="inlineStr">
         <is>
-          <t>1880</t>
+          <t>1892</t>
         </is>
       </c>
       <c r="T13" s="2" t="inlineStr">
         <is>
-          <t>9683</t>
+          <t>8727</t>
         </is>
       </c>
       <c r="U13" s="2" t="inlineStr">
@@ -1851,7 +1851,7 @@
       </c>
       <c r="W13" s="2" t="inlineStr">
         <is>
-          <t>0,69%</t>
+          <t>0,62%</t>
         </is>
       </c>
     </row>
@@ -1874,12 +1874,12 @@
       </c>
       <c r="E14" s="2" t="inlineStr">
         <is>
-          <t>675075</t>
+          <t>675346</t>
         </is>
       </c>
       <c r="F14" s="2" t="inlineStr">
         <is>
-          <t>680360</t>
+          <t>680379</t>
         </is>
       </c>
       <c r="G14" s="2" t="inlineStr">
@@ -1889,12 +1889,12 @@
       </c>
       <c r="H14" s="2" t="inlineStr">
         <is>
-          <t>99,13%</t>
+          <t>99,17%</t>
         </is>
       </c>
       <c r="I14" s="2" t="inlineStr">
         <is>
-          <t>99,9%</t>
+          <t>99,91%</t>
         </is>
       </c>
       <c r="J14" s="2" t="inlineStr">
@@ -1909,12 +1909,12 @@
       </c>
       <c r="L14" s="2" t="inlineStr">
         <is>
-          <t>716310</t>
+          <t>715653</t>
         </is>
       </c>
       <c r="M14" s="2" t="inlineStr">
         <is>
-          <t>721289</t>
+          <t>721288</t>
         </is>
       </c>
       <c r="N14" s="2" t="inlineStr">
@@ -1924,7 +1924,7 @@
       </c>
       <c r="O14" s="2" t="inlineStr">
         <is>
-          <t>99,22%</t>
+          <t>99,12%</t>
         </is>
       </c>
       <c r="P14" s="2" t="inlineStr">
@@ -1944,12 +1944,12 @@
       </c>
       <c r="S14" s="2" t="inlineStr">
         <is>
-          <t>1393312</t>
+          <t>1394268</t>
         </is>
       </c>
       <c r="T14" s="2" t="inlineStr">
         <is>
-          <t>1401115</t>
+          <t>1401103</t>
         </is>
       </c>
       <c r="U14" s="2" t="inlineStr">
@@ -1959,7 +1959,7 @@
       </c>
       <c r="V14" s="2" t="inlineStr">
         <is>
-          <t>99,31%</t>
+          <t>99,38%</t>
         </is>
       </c>
       <c r="W14" s="2" t="inlineStr">
@@ -2375,7 +2375,7 @@
       </c>
       <c r="M4" s="2" t="inlineStr">
         <is>
-          <t>5883</t>
+          <t>6730</t>
         </is>
       </c>
       <c r="N4" s="2" t="inlineStr">
@@ -2390,7 +2390,7 @@
       </c>
       <c r="P4" s="2" t="inlineStr">
         <is>
-          <t>7,04%</t>
+          <t>8,06%</t>
         </is>
       </c>
       <c r="Q4" s="2" t="inlineStr">
@@ -2410,7 +2410,7 @@
       </c>
       <c r="T4" s="2" t="inlineStr">
         <is>
-          <t>6814</t>
+          <t>7882</t>
         </is>
       </c>
       <c r="U4" s="2" t="inlineStr">
@@ -2425,7 +2425,7 @@
       </c>
       <c r="W4" s="2" t="inlineStr">
         <is>
-          <t>3,88%</t>
+          <t>4,49%</t>
         </is>
       </c>
     </row>
@@ -2483,7 +2483,7 @@
       </c>
       <c r="L5" s="2" t="inlineStr">
         <is>
-          <t>77654</t>
+          <t>76807</t>
         </is>
       </c>
       <c r="M5" s="2" t="inlineStr">
@@ -2498,7 +2498,7 @@
       </c>
       <c r="O5" s="2" t="inlineStr">
         <is>
-          <t>92,96%</t>
+          <t>91,94%</t>
         </is>
       </c>
       <c r="P5" s="2" t="inlineStr">
@@ -2518,7 +2518,7 @@
       </c>
       <c r="S5" s="2" t="inlineStr">
         <is>
-          <t>168611</t>
+          <t>167543</t>
         </is>
       </c>
       <c r="T5" s="2" t="inlineStr">
@@ -2533,7 +2533,7 @@
       </c>
       <c r="V5" s="2" t="inlineStr">
         <is>
-          <t>96,12%</t>
+          <t>95,51%</t>
         </is>
       </c>
       <c r="W5" s="2" t="inlineStr">
@@ -2683,7 +2683,7 @@
       </c>
       <c r="F7" s="2" t="inlineStr">
         <is>
-          <t>4767</t>
+          <t>4759</t>
         </is>
       </c>
       <c r="G7" s="2" t="inlineStr">
@@ -2713,12 +2713,12 @@
       </c>
       <c r="L7" s="2" t="inlineStr">
         <is>
-          <t>1805</t>
+          <t>1456</t>
         </is>
       </c>
       <c r="M7" s="2" t="inlineStr">
         <is>
-          <t>8126</t>
+          <t>8616</t>
         </is>
       </c>
       <c r="N7" s="2" t="inlineStr">
@@ -2728,12 +2728,12 @@
       </c>
       <c r="O7" s="2" t="inlineStr">
         <is>
-          <t>0,37%</t>
+          <t>0,3%</t>
         </is>
       </c>
       <c r="P7" s="2" t="inlineStr">
         <is>
-          <t>1,65%</t>
+          <t>1,75%</t>
         </is>
       </c>
       <c r="Q7" s="2" t="inlineStr">
@@ -2748,12 +2748,12 @@
       </c>
       <c r="S7" s="2" t="inlineStr">
         <is>
-          <t>2602</t>
+          <t>2652</t>
         </is>
       </c>
       <c r="T7" s="2" t="inlineStr">
         <is>
-          <t>10764</t>
+          <t>10427</t>
         </is>
       </c>
       <c r="U7" s="2" t="inlineStr">
@@ -2768,7 +2768,7 @@
       </c>
       <c r="W7" s="2" t="inlineStr">
         <is>
-          <t>1,14%</t>
+          <t>1,11%</t>
         </is>
       </c>
     </row>
@@ -2791,7 +2791,7 @@
       </c>
       <c r="E8" s="2" t="inlineStr">
         <is>
-          <t>444933</t>
+          <t>444941</t>
         </is>
       </c>
       <c r="F8" s="2" t="inlineStr">
@@ -2826,12 +2826,12 @@
       </c>
       <c r="L8" s="2" t="inlineStr">
         <is>
-          <t>484278</t>
+          <t>483788</t>
         </is>
       </c>
       <c r="M8" s="2" t="inlineStr">
         <is>
-          <t>490599</t>
+          <t>490948</t>
         </is>
       </c>
       <c r="N8" s="2" t="inlineStr">
@@ -2841,12 +2841,12 @@
       </c>
       <c r="O8" s="2" t="inlineStr">
         <is>
-          <t>98,35%</t>
+          <t>98,25%</t>
         </is>
       </c>
       <c r="P8" s="2" t="inlineStr">
         <is>
-          <t>99,63%</t>
+          <t>99,7%</t>
         </is>
       </c>
       <c r="Q8" s="2" t="inlineStr">
@@ -2861,12 +2861,12 @@
       </c>
       <c r="S8" s="2" t="inlineStr">
         <is>
-          <t>931339</t>
+          <t>931676</t>
         </is>
       </c>
       <c r="T8" s="2" t="inlineStr">
         <is>
-          <t>939501</t>
+          <t>939451</t>
         </is>
       </c>
       <c r="U8" s="2" t="inlineStr">
@@ -2876,7 +2876,7 @@
       </c>
       <c r="V8" s="2" t="inlineStr">
         <is>
-          <t>98,86%</t>
+          <t>98,89%</t>
         </is>
       </c>
       <c r="W8" s="2" t="inlineStr">
@@ -3061,7 +3061,7 @@
       </c>
       <c r="M10" s="2" t="inlineStr">
         <is>
-          <t>3364</t>
+          <t>3865</t>
         </is>
       </c>
       <c r="N10" s="2" t="inlineStr">
@@ -3076,7 +3076,7 @@
       </c>
       <c r="P10" s="2" t="inlineStr">
         <is>
-          <t>1,96%</t>
+          <t>2,25%</t>
         </is>
       </c>
       <c r="Q10" s="2" t="inlineStr">
@@ -3096,7 +3096,7 @@
       </c>
       <c r="T10" s="2" t="inlineStr">
         <is>
-          <t>4266</t>
+          <t>3362</t>
         </is>
       </c>
       <c r="U10" s="2" t="inlineStr">
@@ -3111,7 +3111,7 @@
       </c>
       <c r="W10" s="2" t="inlineStr">
         <is>
-          <t>1,27%</t>
+          <t>1,0%</t>
         </is>
       </c>
     </row>
@@ -3169,7 +3169,7 @@
       </c>
       <c r="L11" s="2" t="inlineStr">
         <is>
-          <t>168197</t>
+          <t>167696</t>
         </is>
       </c>
       <c r="M11" s="2" t="inlineStr">
@@ -3184,7 +3184,7 @@
       </c>
       <c r="O11" s="2" t="inlineStr">
         <is>
-          <t>98,04%</t>
+          <t>97,75%</t>
         </is>
       </c>
       <c r="P11" s="2" t="inlineStr">
@@ -3204,7 +3204,7 @@
       </c>
       <c r="S11" s="2" t="inlineStr">
         <is>
-          <t>332635</t>
+          <t>333539</t>
         </is>
       </c>
       <c r="T11" s="2" t="inlineStr">
@@ -3219,7 +3219,7 @@
       </c>
       <c r="V11" s="2" t="inlineStr">
         <is>
-          <t>98,73%</t>
+          <t>99,0%</t>
         </is>
       </c>
       <c r="W11" s="2" t="inlineStr">
@@ -3369,7 +3369,7 @@
       </c>
       <c r="F13" s="2" t="inlineStr">
         <is>
-          <t>4089</t>
+          <t>4709</t>
         </is>
       </c>
       <c r="G13" s="2" t="inlineStr">
@@ -3384,7 +3384,7 @@
       </c>
       <c r="I13" s="2" t="inlineStr">
         <is>
-          <t>0,58%</t>
+          <t>0,67%</t>
         </is>
       </c>
       <c r="J13" s="2" t="inlineStr">
@@ -3399,12 +3399,12 @@
       </c>
       <c r="L13" s="2" t="inlineStr">
         <is>
-          <t>2679</t>
+          <t>2751</t>
         </is>
       </c>
       <c r="M13" s="2" t="inlineStr">
         <is>
-          <t>11495</t>
+          <t>11600</t>
         </is>
       </c>
       <c r="N13" s="2" t="inlineStr">
@@ -3414,12 +3414,12 @@
       </c>
       <c r="O13" s="2" t="inlineStr">
         <is>
-          <t>0,36%</t>
+          <t>0,37%</t>
         </is>
       </c>
       <c r="P13" s="2" t="inlineStr">
         <is>
-          <t>1,54%</t>
+          <t>1,55%</t>
         </is>
       </c>
       <c r="Q13" s="2" t="inlineStr">
@@ -3434,12 +3434,12 @@
       </c>
       <c r="S13" s="2" t="inlineStr">
         <is>
-          <t>3470</t>
+          <t>3319</t>
         </is>
       </c>
       <c r="T13" s="2" t="inlineStr">
         <is>
-          <t>14109</t>
+          <t>12384</t>
         </is>
       </c>
       <c r="U13" s="2" t="inlineStr">
@@ -3449,12 +3449,12 @@
       </c>
       <c r="V13" s="2" t="inlineStr">
         <is>
-          <t>0,24%</t>
+          <t>0,23%</t>
         </is>
       </c>
       <c r="W13" s="2" t="inlineStr">
         <is>
-          <t>0,97%</t>
+          <t>0,85%</t>
         </is>
       </c>
     </row>
@@ -3477,7 +3477,7 @@
       </c>
       <c r="E14" s="2" t="inlineStr">
         <is>
-          <t>702839</t>
+          <t>702219</t>
         </is>
       </c>
       <c r="F14" s="2" t="inlineStr">
@@ -3492,7 +3492,7 @@
       </c>
       <c r="H14" s="2" t="inlineStr">
         <is>
-          <t>99,42%</t>
+          <t>99,33%</t>
         </is>
       </c>
       <c r="I14" s="2" t="inlineStr">
@@ -3512,12 +3512,12 @@
       </c>
       <c r="L14" s="2" t="inlineStr">
         <is>
-          <t>736006</t>
+          <t>735901</t>
         </is>
       </c>
       <c r="M14" s="2" t="inlineStr">
         <is>
-          <t>744822</t>
+          <t>744750</t>
         </is>
       </c>
       <c r="N14" s="2" t="inlineStr">
@@ -3527,12 +3527,12 @@
       </c>
       <c r="O14" s="2" t="inlineStr">
         <is>
-          <t>98,46%</t>
+          <t>98,45%</t>
         </is>
       </c>
       <c r="P14" s="2" t="inlineStr">
         <is>
-          <t>99,64%</t>
+          <t>99,63%</t>
         </is>
       </c>
       <c r="Q14" s="2" t="inlineStr">
@@ -3547,12 +3547,12 @@
       </c>
       <c r="S14" s="2" t="inlineStr">
         <is>
-          <t>1440320</t>
+          <t>1442045</t>
         </is>
       </c>
       <c r="T14" s="2" t="inlineStr">
         <is>
-          <t>1450959</t>
+          <t>1451110</t>
         </is>
       </c>
       <c r="U14" s="2" t="inlineStr">
@@ -3562,12 +3562,12 @@
       </c>
       <c r="V14" s="2" t="inlineStr">
         <is>
-          <t>99,03%</t>
+          <t>99,15%</t>
         </is>
       </c>
       <c r="W14" s="2" t="inlineStr">
         <is>
-          <t>99,76%</t>
+          <t>99,77%</t>
         </is>
       </c>
     </row>
@@ -3943,7 +3943,7 @@
       </c>
       <c r="F4" s="2" t="inlineStr">
         <is>
-          <t>3612</t>
+          <t>3721</t>
         </is>
       </c>
       <c r="G4" s="2" t="inlineStr">
@@ -3958,7 +3958,7 @@
       </c>
       <c r="I4" s="2" t="inlineStr">
         <is>
-          <t>6,08%</t>
+          <t>6,27%</t>
         </is>
       </c>
       <c r="J4" s="2" t="inlineStr">
@@ -3978,7 +3978,7 @@
       </c>
       <c r="M4" s="2" t="inlineStr">
         <is>
-          <t>3722</t>
+          <t>2623</t>
         </is>
       </c>
       <c r="N4" s="2" t="inlineStr">
@@ -3993,7 +3993,7 @@
       </c>
       <c r="P4" s="2" t="inlineStr">
         <is>
-          <t>5,42%</t>
+          <t>3,82%</t>
         </is>
       </c>
       <c r="Q4" s="2" t="inlineStr">
@@ -4008,12 +4008,12 @@
       </c>
       <c r="S4" s="2" t="inlineStr">
         <is>
-          <t>539</t>
+          <t>529</t>
         </is>
       </c>
       <c r="T4" s="2" t="inlineStr">
         <is>
-          <t>5001</t>
+          <t>4777</t>
         </is>
       </c>
       <c r="U4" s="2" t="inlineStr">
@@ -4023,12 +4023,12 @@
       </c>
       <c r="V4" s="2" t="inlineStr">
         <is>
-          <t>0,42%</t>
+          <t>0,41%</t>
         </is>
       </c>
       <c r="W4" s="2" t="inlineStr">
         <is>
-          <t>3,91%</t>
+          <t>3,73%</t>
         </is>
       </c>
     </row>
@@ -4051,7 +4051,7 @@
       </c>
       <c r="E5" s="2" t="inlineStr">
         <is>
-          <t>55766</t>
+          <t>55657</t>
         </is>
       </c>
       <c r="F5" s="2" t="inlineStr">
@@ -4066,7 +4066,7 @@
       </c>
       <c r="H5" s="2" t="inlineStr">
         <is>
-          <t>93,92%</t>
+          <t>93,73%</t>
         </is>
       </c>
       <c r="I5" s="2" t="inlineStr">
@@ -4086,7 +4086,7 @@
       </c>
       <c r="L5" s="2" t="inlineStr">
         <is>
-          <t>64892</t>
+          <t>65991</t>
         </is>
       </c>
       <c r="M5" s="2" t="inlineStr">
@@ -4101,7 +4101,7 @@
       </c>
       <c r="O5" s="2" t="inlineStr">
         <is>
-          <t>94,58%</t>
+          <t>96,18%</t>
         </is>
       </c>
       <c r="P5" s="2" t="inlineStr">
@@ -4121,12 +4121,12 @@
       </c>
       <c r="S5" s="2" t="inlineStr">
         <is>
-          <t>122992</t>
+          <t>123216</t>
         </is>
       </c>
       <c r="T5" s="2" t="inlineStr">
         <is>
-          <t>127454</t>
+          <t>127464</t>
         </is>
       </c>
       <c r="U5" s="2" t="inlineStr">
@@ -4136,12 +4136,12 @@
       </c>
       <c r="V5" s="2" t="inlineStr">
         <is>
-          <t>96,09%</t>
+          <t>96,27%</t>
         </is>
       </c>
       <c r="W5" s="2" t="inlineStr">
         <is>
-          <t>99,58%</t>
+          <t>99,59%</t>
         </is>
       </c>
     </row>
@@ -4286,7 +4286,7 @@
       </c>
       <c r="F7" s="2" t="inlineStr">
         <is>
-          <t>5366</t>
+          <t>5018</t>
         </is>
       </c>
       <c r="G7" s="2" t="inlineStr">
@@ -4301,7 +4301,7 @@
       </c>
       <c r="I7" s="2" t="inlineStr">
         <is>
-          <t>1,14%</t>
+          <t>1,06%</t>
         </is>
       </c>
       <c r="J7" s="2" t="inlineStr">
@@ -4321,7 +4321,7 @@
       </c>
       <c r="M7" s="2" t="inlineStr">
         <is>
-          <t>4790</t>
+          <t>4328</t>
         </is>
       </c>
       <c r="N7" s="2" t="inlineStr">
@@ -4336,7 +4336,7 @@
       </c>
       <c r="P7" s="2" t="inlineStr">
         <is>
-          <t>0,98%</t>
+          <t>0,89%</t>
         </is>
       </c>
       <c r="Q7" s="2" t="inlineStr">
@@ -4351,12 +4351,12 @@
       </c>
       <c r="S7" s="2" t="inlineStr">
         <is>
-          <t>666</t>
+          <t>665</t>
         </is>
       </c>
       <c r="T7" s="2" t="inlineStr">
         <is>
-          <t>7246</t>
+          <t>6827</t>
         </is>
       </c>
       <c r="U7" s="2" t="inlineStr">
@@ -4371,7 +4371,7 @@
       </c>
       <c r="W7" s="2" t="inlineStr">
         <is>
-          <t>0,75%</t>
+          <t>0,71%</t>
         </is>
       </c>
     </row>
@@ -4394,7 +4394,7 @@
       </c>
       <c r="E8" s="2" t="inlineStr">
         <is>
-          <t>466924</t>
+          <t>467272</t>
         </is>
       </c>
       <c r="F8" s="2" t="inlineStr">
@@ -4409,7 +4409,7 @@
       </c>
       <c r="H8" s="2" t="inlineStr">
         <is>
-          <t>98,86%</t>
+          <t>98,94%</t>
         </is>
       </c>
       <c r="I8" s="2" t="inlineStr">
@@ -4429,7 +4429,7 @@
       </c>
       <c r="L8" s="2" t="inlineStr">
         <is>
-          <t>483945</t>
+          <t>484407</t>
         </is>
       </c>
       <c r="M8" s="2" t="inlineStr">
@@ -4444,7 +4444,7 @@
       </c>
       <c r="O8" s="2" t="inlineStr">
         <is>
-          <t>99,02%</t>
+          <t>99,11%</t>
         </is>
       </c>
       <c r="P8" s="2" t="inlineStr">
@@ -4464,12 +4464,12 @@
       </c>
       <c r="S8" s="2" t="inlineStr">
         <is>
-          <t>953779</t>
+          <t>954198</t>
         </is>
       </c>
       <c r="T8" s="2" t="inlineStr">
         <is>
-          <t>960359</t>
+          <t>960360</t>
         </is>
       </c>
       <c r="U8" s="2" t="inlineStr">
@@ -4479,7 +4479,7 @@
       </c>
       <c r="V8" s="2" t="inlineStr">
         <is>
-          <t>99,25%</t>
+          <t>99,29%</t>
         </is>
       </c>
       <c r="W8" s="2" t="inlineStr">
@@ -4967,12 +4967,12 @@
       </c>
       <c r="E13" s="2" t="inlineStr">
         <is>
-          <t>604</t>
+          <t>658</t>
         </is>
       </c>
       <c r="F13" s="2" t="inlineStr">
         <is>
-          <t>6238</t>
+          <t>6757</t>
         </is>
       </c>
       <c r="G13" s="2" t="inlineStr">
@@ -4987,7 +4987,7 @@
       </c>
       <c r="I13" s="2" t="inlineStr">
         <is>
-          <t>0,89%</t>
+          <t>0,96%</t>
         </is>
       </c>
       <c r="J13" s="2" t="inlineStr">
@@ -5002,12 +5002,12 @@
       </c>
       <c r="L13" s="2" t="inlineStr">
         <is>
-          <t>624</t>
+          <t>626</t>
         </is>
       </c>
       <c r="M13" s="2" t="inlineStr">
         <is>
-          <t>5261</t>
+          <t>5491</t>
         </is>
       </c>
       <c r="N13" s="2" t="inlineStr">
@@ -5022,7 +5022,7 @@
       </c>
       <c r="P13" s="2" t="inlineStr">
         <is>
-          <t>0,71%</t>
+          <t>0,74%</t>
         </is>
       </c>
       <c r="Q13" s="2" t="inlineStr">
@@ -5037,12 +5037,12 @@
       </c>
       <c r="S13" s="2" t="inlineStr">
         <is>
-          <t>1938</t>
+          <t>2001</t>
         </is>
       </c>
       <c r="T13" s="2" t="inlineStr">
         <is>
-          <t>9470</t>
+          <t>9605</t>
         </is>
       </c>
       <c r="U13" s="2" t="inlineStr">
@@ -5052,12 +5052,12 @@
       </c>
       <c r="V13" s="2" t="inlineStr">
         <is>
-          <t>0,13%</t>
+          <t>0,14%</t>
         </is>
       </c>
       <c r="W13" s="2" t="inlineStr">
         <is>
-          <t>0,65%</t>
+          <t>0,66%</t>
         </is>
       </c>
     </row>
@@ -5080,12 +5080,12 @@
       </c>
       <c r="E14" s="2" t="inlineStr">
         <is>
-          <t>698133</t>
+          <t>697614</t>
         </is>
       </c>
       <c r="F14" s="2" t="inlineStr">
         <is>
-          <t>703767</t>
+          <t>703713</t>
         </is>
       </c>
       <c r="G14" s="2" t="inlineStr">
@@ -5095,7 +5095,7 @@
       </c>
       <c r="H14" s="2" t="inlineStr">
         <is>
-          <t>99,11%</t>
+          <t>99,04%</t>
         </is>
       </c>
       <c r="I14" s="2" t="inlineStr">
@@ -5115,12 +5115,12 @@
       </c>
       <c r="L14" s="2" t="inlineStr">
         <is>
-          <t>739583</t>
+          <t>739353</t>
         </is>
       </c>
       <c r="M14" s="2" t="inlineStr">
         <is>
-          <t>744220</t>
+          <t>744218</t>
         </is>
       </c>
       <c r="N14" s="2" t="inlineStr">
@@ -5130,7 +5130,7 @@
       </c>
       <c r="O14" s="2" t="inlineStr">
         <is>
-          <t>99,29%</t>
+          <t>99,26%</t>
         </is>
       </c>
       <c r="P14" s="2" t="inlineStr">
@@ -5150,12 +5150,12 @@
       </c>
       <c r="S14" s="2" t="inlineStr">
         <is>
-          <t>1439745</t>
+          <t>1439610</t>
         </is>
       </c>
       <c r="T14" s="2" t="inlineStr">
         <is>
-          <t>1447277</t>
+          <t>1447214</t>
         </is>
       </c>
       <c r="U14" s="2" t="inlineStr">
@@ -5165,12 +5165,12 @@
       </c>
       <c r="V14" s="2" t="inlineStr">
         <is>
-          <t>99,35%</t>
+          <t>99,34%</t>
         </is>
       </c>
       <c r="W14" s="2" t="inlineStr">
         <is>
-          <t>99,87%</t>
+          <t>99,86%</t>
         </is>
       </c>
     </row>

--- a/data/trans_orig/IP1006-Estudios-trans_orig.xlsx
+++ b/data/trans_orig/IP1006-Estudios-trans_orig.xlsx
@@ -543,7 +543,7 @@
       <c r="B1" s="2" t="n"/>
       <c r="C1" s="3" t="inlineStr">
         <is>
-          <t>Niña</t>
+          <t>Niño</t>
         </is>
       </c>
       <c r="D1" s="3" t="n"/>
@@ -554,7 +554,7 @@
       <c r="I1" s="3" t="n"/>
       <c r="J1" s="3" t="inlineStr">
         <is>
-          <t>Niño</t>
+          <t>Niña</t>
         </is>
       </c>
       <c r="K1" s="3" t="n"/>
@@ -722,107 +722,107 @@
       </c>
       <c r="C4" s="2" t="inlineStr">
         <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="D4" s="2" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="E4" s="2" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="F4" s="2" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="G4" s="2" t="inlineStr">
+        <is>
+          <t>0,0%</t>
+        </is>
+      </c>
+      <c r="H4" s="2" t="inlineStr">
+        <is>
+          <t>—%</t>
+        </is>
+      </c>
+      <c r="I4" s="2" t="inlineStr">
+        <is>
+          <t>—%</t>
+        </is>
+      </c>
+      <c r="J4" s="2" t="inlineStr">
+        <is>
           <t>2</t>
         </is>
       </c>
-      <c r="D4" s="2" t="inlineStr">
+      <c r="K4" s="2" t="inlineStr">
         <is>
           <t>1325</t>
         </is>
       </c>
-      <c r="E4" s="2" t="inlineStr">
+      <c r="L4" s="2" t="inlineStr">
         <is>
           <t>0</t>
         </is>
       </c>
-      <c r="F4" s="2" t="inlineStr">
-        <is>
-          <t>4673</t>
-        </is>
-      </c>
-      <c r="G4" s="2" t="inlineStr">
+      <c r="M4" s="2" t="inlineStr">
+        <is>
+          <t>3995</t>
+        </is>
+      </c>
+      <c r="N4" s="2" t="inlineStr">
         <is>
           <t>1,46%</t>
         </is>
       </c>
-      <c r="H4" s="2" t="inlineStr">
+      <c r="O4" s="2" t="inlineStr">
         <is>
           <t>0,0%</t>
         </is>
       </c>
-      <c r="I4" s="2" t="inlineStr">
-        <is>
-          <t>5,14%</t>
-        </is>
-      </c>
-      <c r="J4" s="2" t="inlineStr">
+      <c r="P4" s="2" t="inlineStr">
+        <is>
+          <t>4,4%</t>
+        </is>
+      </c>
+      <c r="Q4" s="2" t="inlineStr">
+        <is>
+          <t>2</t>
+        </is>
+      </c>
+      <c r="R4" s="2" t="inlineStr">
+        <is>
+          <t>1325</t>
+        </is>
+      </c>
+      <c r="S4" s="2" t="inlineStr">
         <is>
           <t>0</t>
         </is>
       </c>
-      <c r="K4" s="2" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="L4" s="2" t="inlineStr">
-        <is>
-          <t>—</t>
-        </is>
-      </c>
-      <c r="M4" s="2" t="inlineStr">
-        <is>
-          <t>—</t>
-        </is>
-      </c>
-      <c r="N4" s="2" t="inlineStr">
+      <c r="T4" s="2" t="inlineStr">
+        <is>
+          <t>4239</t>
+        </is>
+      </c>
+      <c r="U4" s="2" t="inlineStr">
+        <is>
+          <t>0,75%</t>
+        </is>
+      </c>
+      <c r="V4" s="2" t="inlineStr">
         <is>
           <t>0,0%</t>
         </is>
       </c>
-      <c r="O4" s="2" t="inlineStr">
-        <is>
-          <t>—%</t>
-        </is>
-      </c>
-      <c r="P4" s="2" t="inlineStr">
-        <is>
-          <t>—%</t>
-        </is>
-      </c>
-      <c r="Q4" s="2" t="inlineStr">
-        <is>
-          <t>2</t>
-        </is>
-      </c>
-      <c r="R4" s="2" t="inlineStr">
-        <is>
-          <t>1325</t>
-        </is>
-      </c>
-      <c r="S4" s="2" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="T4" s="2" t="inlineStr">
-        <is>
-          <t>4122</t>
-        </is>
-      </c>
-      <c r="U4" s="2" t="inlineStr">
-        <is>
-          <t>0,75%</t>
-        </is>
-      </c>
-      <c r="V4" s="2" t="inlineStr">
-        <is>
-          <t>0,0%</t>
-        </is>
-      </c>
       <c r="W4" s="2" t="inlineStr">
         <is>
-          <t>2,32%</t>
+          <t>2,39%</t>
         </is>
       </c>
     </row>
@@ -835,74 +835,74 @@
       </c>
       <c r="C5" s="2" t="inlineStr">
         <is>
+          <t>130</t>
+        </is>
+      </c>
+      <c r="D5" s="2" t="inlineStr">
+        <is>
+          <t>86845</t>
+        </is>
+      </c>
+      <c r="E5" s="2" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="F5" s="2" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="G5" s="2" t="inlineStr">
+        <is>
+          <t>100,0%</t>
+        </is>
+      </c>
+      <c r="H5" s="2" t="inlineStr">
+        <is>
+          <t>—%</t>
+        </is>
+      </c>
+      <c r="I5" s="2" t="inlineStr">
+        <is>
+          <t>—%</t>
+        </is>
+      </c>
+      <c r="J5" s="2" t="inlineStr">
+        <is>
           <t>134</t>
         </is>
       </c>
-      <c r="D5" s="2" t="inlineStr">
+      <c r="K5" s="2" t="inlineStr">
         <is>
           <t>89542</t>
         </is>
       </c>
-      <c r="E5" s="2" t="inlineStr">
-        <is>
-          <t>86194</t>
-        </is>
-      </c>
-      <c r="F5" s="2" t="inlineStr">
+      <c r="L5" s="2" t="inlineStr">
+        <is>
+          <t>86872</t>
+        </is>
+      </c>
+      <c r="M5" s="2" t="inlineStr">
         <is>
           <t>90867</t>
         </is>
       </c>
-      <c r="G5" s="2" t="inlineStr">
+      <c r="N5" s="2" t="inlineStr">
         <is>
           <t>98,54%</t>
         </is>
       </c>
-      <c r="H5" s="2" t="inlineStr">
-        <is>
-          <t>94,86%</t>
-        </is>
-      </c>
-      <c r="I5" s="2" t="inlineStr">
+      <c r="O5" s="2" t="inlineStr">
+        <is>
+          <t>95,6%</t>
+        </is>
+      </c>
+      <c r="P5" s="2" t="inlineStr">
         <is>
           <t>100,0%</t>
         </is>
       </c>
-      <c r="J5" s="2" t="inlineStr">
-        <is>
-          <t>130</t>
-        </is>
-      </c>
-      <c r="K5" s="2" t="inlineStr">
-        <is>
-          <t>86845</t>
-        </is>
-      </c>
-      <c r="L5" s="2" t="inlineStr">
-        <is>
-          <t>—</t>
-        </is>
-      </c>
-      <c r="M5" s="2" t="inlineStr">
-        <is>
-          <t>—</t>
-        </is>
-      </c>
-      <c r="N5" s="2" t="inlineStr">
-        <is>
-          <t>100,0%</t>
-        </is>
-      </c>
-      <c r="O5" s="2" t="inlineStr">
-        <is>
-          <t>—%</t>
-        </is>
-      </c>
-      <c r="P5" s="2" t="inlineStr">
-        <is>
-          <t>—%</t>
-        </is>
-      </c>
       <c r="Q5" s="2" t="inlineStr">
         <is>
           <t>264</t>
@@ -915,7 +915,7 @@
       </c>
       <c r="S5" s="2" t="inlineStr">
         <is>
-          <t>173590</t>
+          <t>173473</t>
         </is>
       </c>
       <c r="T5" s="2" t="inlineStr">
@@ -930,7 +930,7 @@
       </c>
       <c r="V5" s="2" t="inlineStr">
         <is>
-          <t>97,68%</t>
+          <t>97,61%</t>
         </is>
       </c>
       <c r="W5" s="2" t="inlineStr">
@@ -948,57 +948,57 @@
       </c>
       <c r="C6" s="2" t="inlineStr">
         <is>
+          <t>130</t>
+        </is>
+      </c>
+      <c r="D6" s="2" t="inlineStr">
+        <is>
+          <t>86845</t>
+        </is>
+      </c>
+      <c r="E6" s="2" t="inlineStr">
+        <is>
+          <t>86845</t>
+        </is>
+      </c>
+      <c r="F6" s="2" t="inlineStr">
+        <is>
+          <t>86845</t>
+        </is>
+      </c>
+      <c r="G6" s="2" t="inlineStr">
+        <is>
+          <t>100%</t>
+        </is>
+      </c>
+      <c r="H6" s="2" t="inlineStr">
+        <is>
+          <t>100%</t>
+        </is>
+      </c>
+      <c r="I6" s="2" t="inlineStr">
+        <is>
+          <t>100%</t>
+        </is>
+      </c>
+      <c r="J6" s="2" t="inlineStr">
+        <is>
           <t>136</t>
         </is>
       </c>
-      <c r="D6" s="2" t="inlineStr">
+      <c r="K6" s="2" t="inlineStr">
         <is>
           <t>90867</t>
         </is>
       </c>
-      <c r="E6" s="2" t="inlineStr">
+      <c r="L6" s="2" t="inlineStr">
         <is>
           <t>90867</t>
         </is>
       </c>
-      <c r="F6" s="2" t="inlineStr">
+      <c r="M6" s="2" t="inlineStr">
         <is>
           <t>90867</t>
-        </is>
-      </c>
-      <c r="G6" s="2" t="inlineStr">
-        <is>
-          <t>100%</t>
-        </is>
-      </c>
-      <c r="H6" s="2" t="inlineStr">
-        <is>
-          <t>100%</t>
-        </is>
-      </c>
-      <c r="I6" s="2" t="inlineStr">
-        <is>
-          <t>100%</t>
-        </is>
-      </c>
-      <c r="J6" s="2" t="inlineStr">
-        <is>
-          <t>130</t>
-        </is>
-      </c>
-      <c r="K6" s="2" t="inlineStr">
-        <is>
-          <t>86845</t>
-        </is>
-      </c>
-      <c r="L6" s="2" t="inlineStr">
-        <is>
-          <t>86845</t>
-        </is>
-      </c>
-      <c r="M6" s="2" t="inlineStr">
-        <is>
-          <t>86845</t>
         </is>
       </c>
       <c r="N6" s="2" t="inlineStr">
@@ -1065,72 +1065,72 @@
       </c>
       <c r="C7" s="2" t="inlineStr">
         <is>
+          <t>3</t>
+        </is>
+      </c>
+      <c r="D7" s="2" t="inlineStr">
+        <is>
+          <t>2100</t>
+        </is>
+      </c>
+      <c r="E7" s="2" t="inlineStr">
+        <is>
+          <t>685</t>
+        </is>
+      </c>
+      <c r="F7" s="2" t="inlineStr">
+        <is>
+          <t>6318</t>
+        </is>
+      </c>
+      <c r="G7" s="2" t="inlineStr">
+        <is>
+          <t>0,44%</t>
+        </is>
+      </c>
+      <c r="H7" s="2" t="inlineStr">
+        <is>
+          <t>0,14%</t>
+        </is>
+      </c>
+      <c r="I7" s="2" t="inlineStr">
+        <is>
+          <t>1,32%</t>
+        </is>
+      </c>
+      <c r="J7" s="2" t="inlineStr">
+        <is>
           <t>1</t>
         </is>
       </c>
-      <c r="D7" s="2" t="inlineStr">
+      <c r="K7" s="2" t="inlineStr">
         <is>
           <t>661</t>
         </is>
       </c>
-      <c r="E7" s="2" t="inlineStr">
+      <c r="L7" s="2" t="inlineStr">
         <is>
           <t>0</t>
         </is>
       </c>
-      <c r="F7" s="2" t="inlineStr">
-        <is>
-          <t>3336</t>
-        </is>
-      </c>
-      <c r="G7" s="2" t="inlineStr">
+      <c r="M7" s="2" t="inlineStr">
+        <is>
+          <t>3572</t>
+        </is>
+      </c>
+      <c r="N7" s="2" t="inlineStr">
         <is>
           <t>0,16%</t>
         </is>
       </c>
-      <c r="H7" s="2" t="inlineStr">
+      <c r="O7" s="2" t="inlineStr">
         <is>
           <t>0,0%</t>
         </is>
       </c>
-      <c r="I7" s="2" t="inlineStr">
-        <is>
-          <t>0,8%</t>
-        </is>
-      </c>
-      <c r="J7" s="2" t="inlineStr">
-        <is>
-          <t>3</t>
-        </is>
-      </c>
-      <c r="K7" s="2" t="inlineStr">
-        <is>
-          <t>2100</t>
-        </is>
-      </c>
-      <c r="L7" s="2" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="M7" s="2" t="inlineStr">
-        <is>
-          <t>5611</t>
-        </is>
-      </c>
-      <c r="N7" s="2" t="inlineStr">
-        <is>
-          <t>0,44%</t>
-        </is>
-      </c>
-      <c r="O7" s="2" t="inlineStr">
-        <is>
-          <t>0,0%</t>
-        </is>
-      </c>
       <c r="P7" s="2" t="inlineStr">
         <is>
-          <t>1,18%</t>
+          <t>0,86%</t>
         </is>
       </c>
       <c r="Q7" s="2" t="inlineStr">
@@ -1145,12 +1145,12 @@
       </c>
       <c r="S7" s="2" t="inlineStr">
         <is>
-          <t>696</t>
+          <t>695</t>
         </is>
       </c>
       <c r="T7" s="2" t="inlineStr">
         <is>
-          <t>6239</t>
+          <t>6994</t>
         </is>
       </c>
       <c r="U7" s="2" t="inlineStr">
@@ -1165,7 +1165,7 @@
       </c>
       <c r="W7" s="2" t="inlineStr">
         <is>
-          <t>0,7%</t>
+          <t>0,78%</t>
         </is>
       </c>
     </row>
@@ -1178,74 +1178,74 @@
       </c>
       <c r="C8" s="2" t="inlineStr">
         <is>
+          <t>716</t>
+        </is>
+      </c>
+      <c r="D8" s="2" t="inlineStr">
+        <is>
+          <t>474891</t>
+        </is>
+      </c>
+      <c r="E8" s="2" t="inlineStr">
+        <is>
+          <t>470673</t>
+        </is>
+      </c>
+      <c r="F8" s="2" t="inlineStr">
+        <is>
+          <t>476306</t>
+        </is>
+      </c>
+      <c r="G8" s="2" t="inlineStr">
+        <is>
+          <t>99,56%</t>
+        </is>
+      </c>
+      <c r="H8" s="2" t="inlineStr">
+        <is>
+          <t>98,68%</t>
+        </is>
+      </c>
+      <c r="I8" s="2" t="inlineStr">
+        <is>
+          <t>99,86%</t>
+        </is>
+      </c>
+      <c r="J8" s="2" t="inlineStr">
+        <is>
           <t>627</t>
         </is>
       </c>
-      <c r="D8" s="2" t="inlineStr">
+      <c r="K8" s="2" t="inlineStr">
         <is>
           <t>415426</t>
         </is>
       </c>
-      <c r="E8" s="2" t="inlineStr">
-        <is>
-          <t>412751</t>
-        </is>
-      </c>
-      <c r="F8" s="2" t="inlineStr">
+      <c r="L8" s="2" t="inlineStr">
+        <is>
+          <t>412515</t>
+        </is>
+      </c>
+      <c r="M8" s="2" t="inlineStr">
         <is>
           <t>416087</t>
         </is>
       </c>
-      <c r="G8" s="2" t="inlineStr">
+      <c r="N8" s="2" t="inlineStr">
         <is>
           <t>99,84%</t>
         </is>
       </c>
-      <c r="H8" s="2" t="inlineStr">
-        <is>
-          <t>99,2%</t>
-        </is>
-      </c>
-      <c r="I8" s="2" t="inlineStr">
+      <c r="O8" s="2" t="inlineStr">
+        <is>
+          <t>99,14%</t>
+        </is>
+      </c>
+      <c r="P8" s="2" t="inlineStr">
         <is>
           <t>100,0%</t>
         </is>
       </c>
-      <c r="J8" s="2" t="inlineStr">
-        <is>
-          <t>716</t>
-        </is>
-      </c>
-      <c r="K8" s="2" t="inlineStr">
-        <is>
-          <t>474891</t>
-        </is>
-      </c>
-      <c r="L8" s="2" t="inlineStr">
-        <is>
-          <t>471380</t>
-        </is>
-      </c>
-      <c r="M8" s="2" t="inlineStr">
-        <is>
-          <t>476991</t>
-        </is>
-      </c>
-      <c r="N8" s="2" t="inlineStr">
-        <is>
-          <t>99,56%</t>
-        </is>
-      </c>
-      <c r="O8" s="2" t="inlineStr">
-        <is>
-          <t>98,82%</t>
-        </is>
-      </c>
-      <c r="P8" s="2" t="inlineStr">
-        <is>
-          <t>100,0%</t>
-        </is>
-      </c>
       <c r="Q8" s="2" t="inlineStr">
         <is>
           <t>1343</t>
@@ -1258,12 +1258,12 @@
       </c>
       <c r="S8" s="2" t="inlineStr">
         <is>
-          <t>886839</t>
+          <t>886084</t>
         </is>
       </c>
       <c r="T8" s="2" t="inlineStr">
         <is>
-          <t>892382</t>
+          <t>892383</t>
         </is>
       </c>
       <c r="U8" s="2" t="inlineStr">
@@ -1273,7 +1273,7 @@
       </c>
       <c r="V8" s="2" t="inlineStr">
         <is>
-          <t>99,3%</t>
+          <t>99,22%</t>
         </is>
       </c>
       <c r="W8" s="2" t="inlineStr">
@@ -1291,57 +1291,57 @@
       </c>
       <c r="C9" s="2" t="inlineStr">
         <is>
+          <t>719</t>
+        </is>
+      </c>
+      <c r="D9" s="2" t="inlineStr">
+        <is>
+          <t>476991</t>
+        </is>
+      </c>
+      <c r="E9" s="2" t="inlineStr">
+        <is>
+          <t>476991</t>
+        </is>
+      </c>
+      <c r="F9" s="2" t="inlineStr">
+        <is>
+          <t>476991</t>
+        </is>
+      </c>
+      <c r="G9" s="2" t="inlineStr">
+        <is>
+          <t>100%</t>
+        </is>
+      </c>
+      <c r="H9" s="2" t="inlineStr">
+        <is>
+          <t>100%</t>
+        </is>
+      </c>
+      <c r="I9" s="2" t="inlineStr">
+        <is>
+          <t>100%</t>
+        </is>
+      </c>
+      <c r="J9" s="2" t="inlineStr">
+        <is>
           <t>628</t>
         </is>
       </c>
-      <c r="D9" s="2" t="inlineStr">
+      <c r="K9" s="2" t="inlineStr">
         <is>
           <t>416087</t>
         </is>
       </c>
-      <c r="E9" s="2" t="inlineStr">
+      <c r="L9" s="2" t="inlineStr">
         <is>
           <t>416087</t>
         </is>
       </c>
-      <c r="F9" s="2" t="inlineStr">
+      <c r="M9" s="2" t="inlineStr">
         <is>
           <t>416087</t>
-        </is>
-      </c>
-      <c r="G9" s="2" t="inlineStr">
-        <is>
-          <t>100%</t>
-        </is>
-      </c>
-      <c r="H9" s="2" t="inlineStr">
-        <is>
-          <t>100%</t>
-        </is>
-      </c>
-      <c r="I9" s="2" t="inlineStr">
-        <is>
-          <t>100%</t>
-        </is>
-      </c>
-      <c r="J9" s="2" t="inlineStr">
-        <is>
-          <t>719</t>
-        </is>
-      </c>
-      <c r="K9" s="2" t="inlineStr">
-        <is>
-          <t>476991</t>
-        </is>
-      </c>
-      <c r="L9" s="2" t="inlineStr">
-        <is>
-          <t>476991</t>
-        </is>
-      </c>
-      <c r="M9" s="2" t="inlineStr">
-        <is>
-          <t>476991</t>
         </is>
       </c>
       <c r="N9" s="2" t="inlineStr">
@@ -1408,107 +1408,107 @@
       </c>
       <c r="C10" s="2" t="inlineStr">
         <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="D10" s="2" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="E10" s="2" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="F10" s="2" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="G10" s="2" t="inlineStr">
+        <is>
+          <t>0,0%</t>
+        </is>
+      </c>
+      <c r="H10" s="2" t="inlineStr">
+        <is>
+          <t>—%</t>
+        </is>
+      </c>
+      <c r="I10" s="2" t="inlineStr">
+        <is>
+          <t>—%</t>
+        </is>
+      </c>
+      <c r="J10" s="2" t="inlineStr">
+        <is>
           <t>1</t>
         </is>
       </c>
-      <c r="D10" s="2" t="inlineStr">
+      <c r="K10" s="2" t="inlineStr">
         <is>
           <t>524</t>
         </is>
       </c>
-      <c r="E10" s="2" t="inlineStr">
+      <c r="L10" s="2" t="inlineStr">
         <is>
           <t>0</t>
         </is>
       </c>
-      <c r="F10" s="2" t="inlineStr">
-        <is>
-          <t>2643</t>
-        </is>
-      </c>
-      <c r="G10" s="2" t="inlineStr">
+      <c r="M10" s="2" t="inlineStr">
+        <is>
+          <t>2630</t>
+        </is>
+      </c>
+      <c r="N10" s="2" t="inlineStr">
         <is>
           <t>0,3%</t>
         </is>
       </c>
-      <c r="H10" s="2" t="inlineStr">
+      <c r="O10" s="2" t="inlineStr">
         <is>
           <t>0,0%</t>
         </is>
       </c>
-      <c r="I10" s="2" t="inlineStr">
-        <is>
-          <t>1,52%</t>
-        </is>
-      </c>
-      <c r="J10" s="2" t="inlineStr">
+      <c r="P10" s="2" t="inlineStr">
+        <is>
+          <t>1,51%</t>
+        </is>
+      </c>
+      <c r="Q10" s="2" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="R10" s="2" t="inlineStr">
+        <is>
+          <t>524</t>
+        </is>
+      </c>
+      <c r="S10" s="2" t="inlineStr">
         <is>
           <t>0</t>
         </is>
       </c>
-      <c r="K10" s="2" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="L10" s="2" t="inlineStr">
-        <is>
-          <t>—</t>
-        </is>
-      </c>
-      <c r="M10" s="2" t="inlineStr">
-        <is>
-          <t>—</t>
-        </is>
-      </c>
-      <c r="N10" s="2" t="inlineStr">
+      <c r="T10" s="2" t="inlineStr">
+        <is>
+          <t>2619</t>
+        </is>
+      </c>
+      <c r="U10" s="2" t="inlineStr">
+        <is>
+          <t>0,16%</t>
+        </is>
+      </c>
+      <c r="V10" s="2" t="inlineStr">
         <is>
           <t>0,0%</t>
         </is>
       </c>
-      <c r="O10" s="2" t="inlineStr">
-        <is>
-          <t>—%</t>
-        </is>
-      </c>
-      <c r="P10" s="2" t="inlineStr">
-        <is>
-          <t>—%</t>
-        </is>
-      </c>
-      <c r="Q10" s="2" t="inlineStr">
-        <is>
-          <t>1</t>
-        </is>
-      </c>
-      <c r="R10" s="2" t="inlineStr">
-        <is>
-          <t>524</t>
-        </is>
-      </c>
-      <c r="S10" s="2" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="T10" s="2" t="inlineStr">
-        <is>
-          <t>2120</t>
-        </is>
-      </c>
-      <c r="U10" s="2" t="inlineStr">
-        <is>
-          <t>0,16%</t>
-        </is>
-      </c>
-      <c r="V10" s="2" t="inlineStr">
-        <is>
-          <t>0,0%</t>
-        </is>
-      </c>
       <c r="W10" s="2" t="inlineStr">
         <is>
-          <t>0,64%</t>
+          <t>0,79%</t>
         </is>
       </c>
     </row>
@@ -1521,74 +1521,74 @@
       </c>
       <c r="C11" s="2" t="inlineStr">
         <is>
+          <t>236</t>
+        </is>
+      </c>
+      <c r="D11" s="2" t="inlineStr">
+        <is>
+          <t>158138</t>
+        </is>
+      </c>
+      <c r="E11" s="2" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="F11" s="2" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="G11" s="2" t="inlineStr">
+        <is>
+          <t>100,0%</t>
+        </is>
+      </c>
+      <c r="H11" s="2" t="inlineStr">
+        <is>
+          <t>—%</t>
+        </is>
+      </c>
+      <c r="I11" s="2" t="inlineStr">
+        <is>
+          <t>—%</t>
+        </is>
+      </c>
+      <c r="J11" s="2" t="inlineStr">
+        <is>
           <t>253</t>
         </is>
       </c>
-      <c r="D11" s="2" t="inlineStr">
+      <c r="K11" s="2" t="inlineStr">
         <is>
           <t>173542</t>
         </is>
       </c>
-      <c r="E11" s="2" t="inlineStr">
-        <is>
-          <t>171423</t>
-        </is>
-      </c>
-      <c r="F11" s="2" t="inlineStr">
+      <c r="L11" s="2" t="inlineStr">
+        <is>
+          <t>171436</t>
+        </is>
+      </c>
+      <c r="M11" s="2" t="inlineStr">
         <is>
           <t>174066</t>
         </is>
       </c>
-      <c r="G11" s="2" t="inlineStr">
+      <c r="N11" s="2" t="inlineStr">
         <is>
           <t>99,7%</t>
         </is>
       </c>
-      <c r="H11" s="2" t="inlineStr">
-        <is>
-          <t>98,48%</t>
-        </is>
-      </c>
-      <c r="I11" s="2" t="inlineStr">
+      <c r="O11" s="2" t="inlineStr">
+        <is>
+          <t>98,49%</t>
+        </is>
+      </c>
+      <c r="P11" s="2" t="inlineStr">
         <is>
           <t>100,0%</t>
         </is>
       </c>
-      <c r="J11" s="2" t="inlineStr">
-        <is>
-          <t>236</t>
-        </is>
-      </c>
-      <c r="K11" s="2" t="inlineStr">
-        <is>
-          <t>158138</t>
-        </is>
-      </c>
-      <c r="L11" s="2" t="inlineStr">
-        <is>
-          <t>—</t>
-        </is>
-      </c>
-      <c r="M11" s="2" t="inlineStr">
-        <is>
-          <t>—</t>
-        </is>
-      </c>
-      <c r="N11" s="2" t="inlineStr">
-        <is>
-          <t>100,0%</t>
-        </is>
-      </c>
-      <c r="O11" s="2" t="inlineStr">
-        <is>
-          <t>—%</t>
-        </is>
-      </c>
-      <c r="P11" s="2" t="inlineStr">
-        <is>
-          <t>—%</t>
-        </is>
-      </c>
       <c r="Q11" s="2" t="inlineStr">
         <is>
           <t>489</t>
@@ -1601,7 +1601,7 @@
       </c>
       <c r="S11" s="2" t="inlineStr">
         <is>
-          <t>330085</t>
+          <t>329586</t>
         </is>
       </c>
       <c r="T11" s="2" t="inlineStr">
@@ -1616,7 +1616,7 @@
       </c>
       <c r="V11" s="2" t="inlineStr">
         <is>
-          <t>99,36%</t>
+          <t>99,21%</t>
         </is>
       </c>
       <c r="W11" s="2" t="inlineStr">
@@ -1634,57 +1634,57 @@
       </c>
       <c r="C12" s="2" t="inlineStr">
         <is>
+          <t>236</t>
+        </is>
+      </c>
+      <c r="D12" s="2" t="inlineStr">
+        <is>
+          <t>158138</t>
+        </is>
+      </c>
+      <c r="E12" s="2" t="inlineStr">
+        <is>
+          <t>158138</t>
+        </is>
+      </c>
+      <c r="F12" s="2" t="inlineStr">
+        <is>
+          <t>158138</t>
+        </is>
+      </c>
+      <c r="G12" s="2" t="inlineStr">
+        <is>
+          <t>100%</t>
+        </is>
+      </c>
+      <c r="H12" s="2" t="inlineStr">
+        <is>
+          <t>100%</t>
+        </is>
+      </c>
+      <c r="I12" s="2" t="inlineStr">
+        <is>
+          <t>100%</t>
+        </is>
+      </c>
+      <c r="J12" s="2" t="inlineStr">
+        <is>
           <t>254</t>
         </is>
       </c>
-      <c r="D12" s="2" t="inlineStr">
+      <c r="K12" s="2" t="inlineStr">
         <is>
           <t>174066</t>
         </is>
       </c>
-      <c r="E12" s="2" t="inlineStr">
+      <c r="L12" s="2" t="inlineStr">
         <is>
           <t>174066</t>
         </is>
       </c>
-      <c r="F12" s="2" t="inlineStr">
+      <c r="M12" s="2" t="inlineStr">
         <is>
           <t>174066</t>
-        </is>
-      </c>
-      <c r="G12" s="2" t="inlineStr">
-        <is>
-          <t>100%</t>
-        </is>
-      </c>
-      <c r="H12" s="2" t="inlineStr">
-        <is>
-          <t>100%</t>
-        </is>
-      </c>
-      <c r="I12" s="2" t="inlineStr">
-        <is>
-          <t>100%</t>
-        </is>
-      </c>
-      <c r="J12" s="2" t="inlineStr">
-        <is>
-          <t>236</t>
-        </is>
-      </c>
-      <c r="K12" s="2" t="inlineStr">
-        <is>
-          <t>158138</t>
-        </is>
-      </c>
-      <c r="L12" s="2" t="inlineStr">
-        <is>
-          <t>158138</t>
-        </is>
-      </c>
-      <c r="M12" s="2" t="inlineStr">
-        <is>
-          <t>158138</t>
         </is>
       </c>
       <c r="N12" s="2" t="inlineStr">
@@ -1751,72 +1751,72 @@
       </c>
       <c r="C13" s="2" t="inlineStr">
         <is>
+          <t>3</t>
+        </is>
+      </c>
+      <c r="D13" s="2" t="inlineStr">
+        <is>
+          <t>2100</t>
+        </is>
+      </c>
+      <c r="E13" s="2" t="inlineStr">
+        <is>
+          <t>684</t>
+        </is>
+      </c>
+      <c r="F13" s="2" t="inlineStr">
+        <is>
+          <t>6292</t>
+        </is>
+      </c>
+      <c r="G13" s="2" t="inlineStr">
+        <is>
+          <t>0,29%</t>
+        </is>
+      </c>
+      <c r="H13" s="2" t="inlineStr">
+        <is>
+          <t>0,09%</t>
+        </is>
+      </c>
+      <c r="I13" s="2" t="inlineStr">
+        <is>
+          <t>0,87%</t>
+        </is>
+      </c>
+      <c r="J13" s="2" t="inlineStr">
+        <is>
           <t>4</t>
         </is>
       </c>
-      <c r="D13" s="2" t="inlineStr">
+      <c r="K13" s="2" t="inlineStr">
         <is>
           <t>2510</t>
         </is>
       </c>
-      <c r="E13" s="2" t="inlineStr">
-        <is>
-          <t>642</t>
-        </is>
-      </c>
-      <c r="F13" s="2" t="inlineStr">
-        <is>
-          <t>5675</t>
-        </is>
-      </c>
-      <c r="G13" s="2" t="inlineStr">
+      <c r="L13" s="2" t="inlineStr">
+        <is>
+          <t>665</t>
+        </is>
+      </c>
+      <c r="M13" s="2" t="inlineStr">
+        <is>
+          <t>6411</t>
+        </is>
+      </c>
+      <c r="N13" s="2" t="inlineStr">
         <is>
           <t>0,37%</t>
         </is>
       </c>
-      <c r="H13" s="2" t="inlineStr">
-        <is>
-          <t>0,09%</t>
-        </is>
-      </c>
-      <c r="I13" s="2" t="inlineStr">
-        <is>
-          <t>0,83%</t>
-        </is>
-      </c>
-      <c r="J13" s="2" t="inlineStr">
-        <is>
-          <t>3</t>
-        </is>
-      </c>
-      <c r="K13" s="2" t="inlineStr">
-        <is>
-          <t>2100</t>
-        </is>
-      </c>
-      <c r="L13" s="2" t="inlineStr">
-        <is>
-          <t>686</t>
-        </is>
-      </c>
-      <c r="M13" s="2" t="inlineStr">
-        <is>
-          <t>6321</t>
-        </is>
-      </c>
-      <c r="N13" s="2" t="inlineStr">
-        <is>
-          <t>0,29%</t>
-        </is>
-      </c>
       <c r="O13" s="2" t="inlineStr">
         <is>
-          <t>0,09%</t>
+          <t>0,1%</t>
         </is>
       </c>
       <c r="P13" s="2" t="inlineStr">
         <is>
-          <t>0,88%</t>
+          <t>0,94%</t>
         </is>
       </c>
       <c r="Q13" s="2" t="inlineStr">
@@ -1831,12 +1831,12 @@
       </c>
       <c r="S13" s="2" t="inlineStr">
         <is>
-          <t>1892</t>
+          <t>1976</t>
         </is>
       </c>
       <c r="T13" s="2" t="inlineStr">
         <is>
-          <t>8727</t>
+          <t>9081</t>
         </is>
       </c>
       <c r="U13" s="2" t="inlineStr">
@@ -1846,12 +1846,12 @@
       </c>
       <c r="V13" s="2" t="inlineStr">
         <is>
-          <t>0,13%</t>
+          <t>0,14%</t>
         </is>
       </c>
       <c r="W13" s="2" t="inlineStr">
         <is>
-          <t>0,62%</t>
+          <t>0,65%</t>
         </is>
       </c>
     </row>
@@ -1864,72 +1864,72 @@
       </c>
       <c r="C14" s="2" t="inlineStr">
         <is>
+          <t>1082</t>
+        </is>
+      </c>
+      <c r="D14" s="2" t="inlineStr">
+        <is>
+          <t>719874</t>
+        </is>
+      </c>
+      <c r="E14" s="2" t="inlineStr">
+        <is>
+          <t>715682</t>
+        </is>
+      </c>
+      <c r="F14" s="2" t="inlineStr">
+        <is>
+          <t>721290</t>
+        </is>
+      </c>
+      <c r="G14" s="2" t="inlineStr">
+        <is>
+          <t>99,71%</t>
+        </is>
+      </c>
+      <c r="H14" s="2" t="inlineStr">
+        <is>
+          <t>99,13%</t>
+        </is>
+      </c>
+      <c r="I14" s="2" t="inlineStr">
+        <is>
+          <t>99,91%</t>
+        </is>
+      </c>
+      <c r="J14" s="2" t="inlineStr">
+        <is>
           <t>1014</t>
         </is>
       </c>
-      <c r="D14" s="2" t="inlineStr">
+      <c r="K14" s="2" t="inlineStr">
         <is>
           <t>678511</t>
         </is>
       </c>
-      <c r="E14" s="2" t="inlineStr">
-        <is>
-          <t>675346</t>
-        </is>
-      </c>
-      <c r="F14" s="2" t="inlineStr">
-        <is>
-          <t>680379</t>
-        </is>
-      </c>
-      <c r="G14" s="2" t="inlineStr">
+      <c r="L14" s="2" t="inlineStr">
+        <is>
+          <t>674610</t>
+        </is>
+      </c>
+      <c r="M14" s="2" t="inlineStr">
+        <is>
+          <t>680356</t>
+        </is>
+      </c>
+      <c r="N14" s="2" t="inlineStr">
         <is>
           <t>99,63%</t>
         </is>
       </c>
-      <c r="H14" s="2" t="inlineStr">
-        <is>
-          <t>99,17%</t>
-        </is>
-      </c>
-      <c r="I14" s="2" t="inlineStr">
-        <is>
-          <t>99,91%</t>
-        </is>
-      </c>
-      <c r="J14" s="2" t="inlineStr">
-        <is>
-          <t>1082</t>
-        </is>
-      </c>
-      <c r="K14" s="2" t="inlineStr">
-        <is>
-          <t>719874</t>
-        </is>
-      </c>
-      <c r="L14" s="2" t="inlineStr">
-        <is>
-          <t>715653</t>
-        </is>
-      </c>
-      <c r="M14" s="2" t="inlineStr">
-        <is>
-          <t>721288</t>
-        </is>
-      </c>
-      <c r="N14" s="2" t="inlineStr">
-        <is>
-          <t>99,71%</t>
-        </is>
-      </c>
       <c r="O14" s="2" t="inlineStr">
         <is>
-          <t>99,12%</t>
+          <t>99,06%</t>
         </is>
       </c>
       <c r="P14" s="2" t="inlineStr">
         <is>
-          <t>99,91%</t>
+          <t>99,9%</t>
         </is>
       </c>
       <c r="Q14" s="2" t="inlineStr">
@@ -1944,12 +1944,12 @@
       </c>
       <c r="S14" s="2" t="inlineStr">
         <is>
-          <t>1394268</t>
+          <t>1393914</t>
         </is>
       </c>
       <c r="T14" s="2" t="inlineStr">
         <is>
-          <t>1401103</t>
+          <t>1401019</t>
         </is>
       </c>
       <c r="U14" s="2" t="inlineStr">
@@ -1959,12 +1959,12 @@
       </c>
       <c r="V14" s="2" t="inlineStr">
         <is>
-          <t>99,38%</t>
+          <t>99,35%</t>
         </is>
       </c>
       <c r="W14" s="2" t="inlineStr">
         <is>
-          <t>99,87%</t>
+          <t>99,86%</t>
         </is>
       </c>
     </row>
@@ -1977,57 +1977,57 @@
       </c>
       <c r="C15" s="2" t="inlineStr">
         <is>
+          <t>1085</t>
+        </is>
+      </c>
+      <c r="D15" s="2" t="inlineStr">
+        <is>
+          <t>721974</t>
+        </is>
+      </c>
+      <c r="E15" s="2" t="inlineStr">
+        <is>
+          <t>721974</t>
+        </is>
+      </c>
+      <c r="F15" s="2" t="inlineStr">
+        <is>
+          <t>721974</t>
+        </is>
+      </c>
+      <c r="G15" s="2" t="inlineStr">
+        <is>
+          <t>100%</t>
+        </is>
+      </c>
+      <c r="H15" s="2" t="inlineStr">
+        <is>
+          <t>100%</t>
+        </is>
+      </c>
+      <c r="I15" s="2" t="inlineStr">
+        <is>
+          <t>100%</t>
+        </is>
+      </c>
+      <c r="J15" s="2" t="inlineStr">
+        <is>
           <t>1018</t>
         </is>
       </c>
-      <c r="D15" s="2" t="inlineStr">
+      <c r="K15" s="2" t="inlineStr">
         <is>
           <t>681021</t>
         </is>
       </c>
-      <c r="E15" s="2" t="inlineStr">
+      <c r="L15" s="2" t="inlineStr">
         <is>
           <t>681021</t>
         </is>
       </c>
-      <c r="F15" s="2" t="inlineStr">
+      <c r="M15" s="2" t="inlineStr">
         <is>
           <t>681021</t>
-        </is>
-      </c>
-      <c r="G15" s="2" t="inlineStr">
-        <is>
-          <t>100%</t>
-        </is>
-      </c>
-      <c r="H15" s="2" t="inlineStr">
-        <is>
-          <t>100%</t>
-        </is>
-      </c>
-      <c r="I15" s="2" t="inlineStr">
-        <is>
-          <t>100%</t>
-        </is>
-      </c>
-      <c r="J15" s="2" t="inlineStr">
-        <is>
-          <t>1085</t>
-        </is>
-      </c>
-      <c r="K15" s="2" t="inlineStr">
-        <is>
-          <t>721974</t>
-        </is>
-      </c>
-      <c r="L15" s="2" t="inlineStr">
-        <is>
-          <t>721974</t>
-        </is>
-      </c>
-      <c r="M15" s="2" t="inlineStr">
-        <is>
-          <t>721974</t>
         </is>
       </c>
       <c r="N15" s="2" t="inlineStr">
@@ -2146,7 +2146,7 @@
       <c r="B1" s="2" t="n"/>
       <c r="C1" s="3" t="inlineStr">
         <is>
-          <t>Niña</t>
+          <t>Niño</t>
         </is>
       </c>
       <c r="D1" s="3" t="n"/>
@@ -2157,7 +2157,7 @@
       <c r="I1" s="3" t="n"/>
       <c r="J1" s="3" t="inlineStr">
         <is>
-          <t>Niño</t>
+          <t>Niña</t>
         </is>
       </c>
       <c r="K1" s="3" t="n"/>
@@ -2325,107 +2325,107 @@
       </c>
       <c r="C4" s="2" t="inlineStr">
         <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="D4" s="2" t="inlineStr">
+        <is>
+          <t>1155</t>
+        </is>
+      </c>
+      <c r="E4" s="2" t="inlineStr">
+        <is>
           <t>0</t>
         </is>
       </c>
-      <c r="D4" s="2" t="inlineStr">
+      <c r="F4" s="2" t="inlineStr">
+        <is>
+          <t>6689</t>
+        </is>
+      </c>
+      <c r="G4" s="2" t="inlineStr">
+        <is>
+          <t>1,38%</t>
+        </is>
+      </c>
+      <c r="H4" s="2" t="inlineStr">
+        <is>
+          <t>0,0%</t>
+        </is>
+      </c>
+      <c r="I4" s="2" t="inlineStr">
+        <is>
+          <t>8,01%</t>
+        </is>
+      </c>
+      <c r="J4" s="2" t="inlineStr">
         <is>
           <t>0</t>
         </is>
       </c>
-      <c r="E4" s="2" t="inlineStr">
+      <c r="K4" s="2" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="L4" s="2" t="inlineStr">
         <is>
           <t>—</t>
         </is>
       </c>
-      <c r="F4" s="2" t="inlineStr">
+      <c r="M4" s="2" t="inlineStr">
         <is>
           <t>—</t>
         </is>
       </c>
-      <c r="G4" s="2" t="inlineStr">
+      <c r="N4" s="2" t="inlineStr">
         <is>
           <t>0,0%</t>
         </is>
       </c>
-      <c r="H4" s="2" t="inlineStr">
+      <c r="O4" s="2" t="inlineStr">
         <is>
           <t>—%</t>
         </is>
       </c>
-      <c r="I4" s="2" t="inlineStr">
+      <c r="P4" s="2" t="inlineStr">
         <is>
           <t>—%</t>
         </is>
       </c>
-      <c r="J4" s="2" t="inlineStr">
+      <c r="Q4" s="2" t="inlineStr">
         <is>
           <t>1</t>
         </is>
       </c>
-      <c r="K4" s="2" t="inlineStr">
+      <c r="R4" s="2" t="inlineStr">
         <is>
           <t>1155</t>
         </is>
       </c>
-      <c r="L4" s="2" t="inlineStr">
+      <c r="S4" s="2" t="inlineStr">
         <is>
           <t>0</t>
         </is>
       </c>
-      <c r="M4" s="2" t="inlineStr">
-        <is>
-          <t>6730</t>
-        </is>
-      </c>
-      <c r="N4" s="2" t="inlineStr">
-        <is>
-          <t>1,38%</t>
-        </is>
-      </c>
-      <c r="O4" s="2" t="inlineStr">
+      <c r="T4" s="2" t="inlineStr">
+        <is>
+          <t>5418</t>
+        </is>
+      </c>
+      <c r="U4" s="2" t="inlineStr">
+        <is>
+          <t>0,66%</t>
+        </is>
+      </c>
+      <c r="V4" s="2" t="inlineStr">
         <is>
           <t>0,0%</t>
         </is>
       </c>
-      <c r="P4" s="2" t="inlineStr">
-        <is>
-          <t>8,06%</t>
-        </is>
-      </c>
-      <c r="Q4" s="2" t="inlineStr">
-        <is>
-          <t>1</t>
-        </is>
-      </c>
-      <c r="R4" s="2" t="inlineStr">
-        <is>
-          <t>1155</t>
-        </is>
-      </c>
-      <c r="S4" s="2" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="T4" s="2" t="inlineStr">
-        <is>
-          <t>7882</t>
-        </is>
-      </c>
-      <c r="U4" s="2" t="inlineStr">
-        <is>
-          <t>0,66%</t>
-        </is>
-      </c>
-      <c r="V4" s="2" t="inlineStr">
-        <is>
-          <t>0,0%</t>
-        </is>
-      </c>
       <c r="W4" s="2" t="inlineStr">
         <is>
-          <t>4,49%</t>
+          <t>3,09%</t>
         </is>
       </c>
     </row>
@@ -2438,74 +2438,74 @@
       </c>
       <c r="C5" s="2" t="inlineStr">
         <is>
+          <t>116</t>
+        </is>
+      </c>
+      <c r="D5" s="2" t="inlineStr">
+        <is>
+          <t>82382</t>
+        </is>
+      </c>
+      <c r="E5" s="2" t="inlineStr">
+        <is>
+          <t>76848</t>
+        </is>
+      </c>
+      <c r="F5" s="2" t="inlineStr">
+        <is>
+          <t>83537</t>
+        </is>
+      </c>
+      <c r="G5" s="2" t="inlineStr">
+        <is>
+          <t>98,62%</t>
+        </is>
+      </c>
+      <c r="H5" s="2" t="inlineStr">
+        <is>
+          <t>91,99%</t>
+        </is>
+      </c>
+      <c r="I5" s="2" t="inlineStr">
+        <is>
+          <t>100,0%</t>
+        </is>
+      </c>
+      <c r="J5" s="2" t="inlineStr">
+        <is>
           <t>133</t>
         </is>
       </c>
-      <c r="D5" s="2" t="inlineStr">
+      <c r="K5" s="2" t="inlineStr">
         <is>
           <t>91889</t>
         </is>
       </c>
-      <c r="E5" s="2" t="inlineStr">
+      <c r="L5" s="2" t="inlineStr">
         <is>
           <t>—</t>
         </is>
       </c>
-      <c r="F5" s="2" t="inlineStr">
+      <c r="M5" s="2" t="inlineStr">
         <is>
           <t>—</t>
         </is>
       </c>
-      <c r="G5" s="2" t="inlineStr">
+      <c r="N5" s="2" t="inlineStr">
         <is>
           <t>100,0%</t>
         </is>
       </c>
-      <c r="H5" s="2" t="inlineStr">
+      <c r="O5" s="2" t="inlineStr">
         <is>
           <t>—%</t>
         </is>
       </c>
-      <c r="I5" s="2" t="inlineStr">
+      <c r="P5" s="2" t="inlineStr">
         <is>
           <t>—%</t>
         </is>
       </c>
-      <c r="J5" s="2" t="inlineStr">
-        <is>
-          <t>116</t>
-        </is>
-      </c>
-      <c r="K5" s="2" t="inlineStr">
-        <is>
-          <t>82382</t>
-        </is>
-      </c>
-      <c r="L5" s="2" t="inlineStr">
-        <is>
-          <t>76807</t>
-        </is>
-      </c>
-      <c r="M5" s="2" t="inlineStr">
-        <is>
-          <t>83537</t>
-        </is>
-      </c>
-      <c r="N5" s="2" t="inlineStr">
-        <is>
-          <t>98,62%</t>
-        </is>
-      </c>
-      <c r="O5" s="2" t="inlineStr">
-        <is>
-          <t>91,94%</t>
-        </is>
-      </c>
-      <c r="P5" s="2" t="inlineStr">
-        <is>
-          <t>100,0%</t>
-        </is>
-      </c>
       <c r="Q5" s="2" t="inlineStr">
         <is>
           <t>249</t>
@@ -2518,7 +2518,7 @@
       </c>
       <c r="S5" s="2" t="inlineStr">
         <is>
-          <t>167543</t>
+          <t>170007</t>
         </is>
       </c>
       <c r="T5" s="2" t="inlineStr">
@@ -2533,7 +2533,7 @@
       </c>
       <c r="V5" s="2" t="inlineStr">
         <is>
-          <t>95,51%</t>
+          <t>96,91%</t>
         </is>
       </c>
       <c r="W5" s="2" t="inlineStr">
@@ -2551,57 +2551,57 @@
       </c>
       <c r="C6" s="2" t="inlineStr">
         <is>
+          <t>117</t>
+        </is>
+      </c>
+      <c r="D6" s="2" t="inlineStr">
+        <is>
+          <t>83537</t>
+        </is>
+      </c>
+      <c r="E6" s="2" t="inlineStr">
+        <is>
+          <t>83537</t>
+        </is>
+      </c>
+      <c r="F6" s="2" t="inlineStr">
+        <is>
+          <t>83537</t>
+        </is>
+      </c>
+      <c r="G6" s="2" t="inlineStr">
+        <is>
+          <t>100%</t>
+        </is>
+      </c>
+      <c r="H6" s="2" t="inlineStr">
+        <is>
+          <t>100%</t>
+        </is>
+      </c>
+      <c r="I6" s="2" t="inlineStr">
+        <is>
+          <t>100%</t>
+        </is>
+      </c>
+      <c r="J6" s="2" t="inlineStr">
+        <is>
           <t>133</t>
         </is>
       </c>
-      <c r="D6" s="2" t="inlineStr">
+      <c r="K6" s="2" t="inlineStr">
         <is>
           <t>91889</t>
         </is>
       </c>
-      <c r="E6" s="2" t="inlineStr">
+      <c r="L6" s="2" t="inlineStr">
         <is>
           <t>91889</t>
         </is>
       </c>
-      <c r="F6" s="2" t="inlineStr">
+      <c r="M6" s="2" t="inlineStr">
         <is>
           <t>91889</t>
-        </is>
-      </c>
-      <c r="G6" s="2" t="inlineStr">
-        <is>
-          <t>100%</t>
-        </is>
-      </c>
-      <c r="H6" s="2" t="inlineStr">
-        <is>
-          <t>100%</t>
-        </is>
-      </c>
-      <c r="I6" s="2" t="inlineStr">
-        <is>
-          <t>100%</t>
-        </is>
-      </c>
-      <c r="J6" s="2" t="inlineStr">
-        <is>
-          <t>117</t>
-        </is>
-      </c>
-      <c r="K6" s="2" t="inlineStr">
-        <is>
-          <t>83537</t>
-        </is>
-      </c>
-      <c r="L6" s="2" t="inlineStr">
-        <is>
-          <t>83537</t>
-        </is>
-      </c>
-      <c r="M6" s="2" t="inlineStr">
-        <is>
-          <t>83537</t>
         </is>
       </c>
       <c r="N6" s="2" t="inlineStr">
@@ -2668,74 +2668,74 @@
       </c>
       <c r="C7" s="2" t="inlineStr">
         <is>
+          <t>6</t>
+        </is>
+      </c>
+      <c r="D7" s="2" t="inlineStr">
+        <is>
+          <t>4066</t>
+        </is>
+      </c>
+      <c r="E7" s="2" t="inlineStr">
+        <is>
+          <t>1361</t>
+        </is>
+      </c>
+      <c r="F7" s="2" t="inlineStr">
+        <is>
+          <t>8147</t>
+        </is>
+      </c>
+      <c r="G7" s="2" t="inlineStr">
+        <is>
+          <t>0,83%</t>
+        </is>
+      </c>
+      <c r="H7" s="2" t="inlineStr">
+        <is>
+          <t>0,28%</t>
+        </is>
+      </c>
+      <c r="I7" s="2" t="inlineStr">
+        <is>
+          <t>1,65%</t>
+        </is>
+      </c>
+      <c r="J7" s="2" t="inlineStr">
+        <is>
           <t>2</t>
         </is>
       </c>
-      <c r="D7" s="2" t="inlineStr">
+      <c r="K7" s="2" t="inlineStr">
         <is>
           <t>1346</t>
         </is>
       </c>
-      <c r="E7" s="2" t="inlineStr">
+      <c r="L7" s="2" t="inlineStr">
         <is>
           <t>0</t>
         </is>
       </c>
-      <c r="F7" s="2" t="inlineStr">
-        <is>
-          <t>4759</t>
-        </is>
-      </c>
-      <c r="G7" s="2" t="inlineStr">
+      <c r="M7" s="2" t="inlineStr">
+        <is>
+          <t>4755</t>
+        </is>
+      </c>
+      <c r="N7" s="2" t="inlineStr">
         <is>
           <t>0,3%</t>
         </is>
       </c>
-      <c r="H7" s="2" t="inlineStr">
+      <c r="O7" s="2" t="inlineStr">
         <is>
           <t>0,0%</t>
         </is>
       </c>
-      <c r="I7" s="2" t="inlineStr">
+      <c r="P7" s="2" t="inlineStr">
         <is>
           <t>1,06%</t>
         </is>
       </c>
-      <c r="J7" s="2" t="inlineStr">
-        <is>
-          <t>6</t>
-        </is>
-      </c>
-      <c r="K7" s="2" t="inlineStr">
-        <is>
-          <t>4066</t>
-        </is>
-      </c>
-      <c r="L7" s="2" t="inlineStr">
-        <is>
-          <t>1456</t>
-        </is>
-      </c>
-      <c r="M7" s="2" t="inlineStr">
-        <is>
-          <t>8616</t>
-        </is>
-      </c>
-      <c r="N7" s="2" t="inlineStr">
-        <is>
-          <t>0,83%</t>
-        </is>
-      </c>
-      <c r="O7" s="2" t="inlineStr">
-        <is>
-          <t>0,3%</t>
-        </is>
-      </c>
-      <c r="P7" s="2" t="inlineStr">
-        <is>
-          <t>1,75%</t>
-        </is>
-      </c>
       <c r="Q7" s="2" t="inlineStr">
         <is>
           <t>8</t>
@@ -2748,12 +2748,12 @@
       </c>
       <c r="S7" s="2" t="inlineStr">
         <is>
-          <t>2652</t>
+          <t>2171</t>
         </is>
       </c>
       <c r="T7" s="2" t="inlineStr">
         <is>
-          <t>10427</t>
+          <t>10830</t>
         </is>
       </c>
       <c r="U7" s="2" t="inlineStr">
@@ -2763,12 +2763,12 @@
       </c>
       <c r="V7" s="2" t="inlineStr">
         <is>
-          <t>0,28%</t>
+          <t>0,23%</t>
         </is>
       </c>
       <c r="W7" s="2" t="inlineStr">
         <is>
-          <t>1,11%</t>
+          <t>1,15%</t>
         </is>
       </c>
     </row>
@@ -2781,74 +2781,74 @@
       </c>
       <c r="C8" s="2" t="inlineStr">
         <is>
+          <t>699</t>
+        </is>
+      </c>
+      <c r="D8" s="2" t="inlineStr">
+        <is>
+          <t>488338</t>
+        </is>
+      </c>
+      <c r="E8" s="2" t="inlineStr">
+        <is>
+          <t>484257</t>
+        </is>
+      </c>
+      <c r="F8" s="2" t="inlineStr">
+        <is>
+          <t>491043</t>
+        </is>
+      </c>
+      <c r="G8" s="2" t="inlineStr">
+        <is>
+          <t>99,17%</t>
+        </is>
+      </c>
+      <c r="H8" s="2" t="inlineStr">
+        <is>
+          <t>98,35%</t>
+        </is>
+      </c>
+      <c r="I8" s="2" t="inlineStr">
+        <is>
+          <t>99,72%</t>
+        </is>
+      </c>
+      <c r="J8" s="2" t="inlineStr">
+        <is>
           <t>649</t>
         </is>
       </c>
-      <c r="D8" s="2" t="inlineStr">
+      <c r="K8" s="2" t="inlineStr">
         <is>
           <t>448354</t>
         </is>
       </c>
-      <c r="E8" s="2" t="inlineStr">
-        <is>
-          <t>444941</t>
-        </is>
-      </c>
-      <c r="F8" s="2" t="inlineStr">
+      <c r="L8" s="2" t="inlineStr">
+        <is>
+          <t>444945</t>
+        </is>
+      </c>
+      <c r="M8" s="2" t="inlineStr">
         <is>
           <t>449700</t>
         </is>
       </c>
-      <c r="G8" s="2" t="inlineStr">
+      <c r="N8" s="2" t="inlineStr">
         <is>
           <t>99,7%</t>
         </is>
       </c>
-      <c r="H8" s="2" t="inlineStr">
+      <c r="O8" s="2" t="inlineStr">
         <is>
           <t>98,94%</t>
         </is>
       </c>
-      <c r="I8" s="2" t="inlineStr">
+      <c r="P8" s="2" t="inlineStr">
         <is>
           <t>100,0%</t>
         </is>
       </c>
-      <c r="J8" s="2" t="inlineStr">
-        <is>
-          <t>699</t>
-        </is>
-      </c>
-      <c r="K8" s="2" t="inlineStr">
-        <is>
-          <t>488338</t>
-        </is>
-      </c>
-      <c r="L8" s="2" t="inlineStr">
-        <is>
-          <t>483788</t>
-        </is>
-      </c>
-      <c r="M8" s="2" t="inlineStr">
-        <is>
-          <t>490948</t>
-        </is>
-      </c>
-      <c r="N8" s="2" t="inlineStr">
-        <is>
-          <t>99,17%</t>
-        </is>
-      </c>
-      <c r="O8" s="2" t="inlineStr">
-        <is>
-          <t>98,25%</t>
-        </is>
-      </c>
-      <c r="P8" s="2" t="inlineStr">
-        <is>
-          <t>99,7%</t>
-        </is>
-      </c>
       <c r="Q8" s="2" t="inlineStr">
         <is>
           <t>1348</t>
@@ -2861,12 +2861,12 @@
       </c>
       <c r="S8" s="2" t="inlineStr">
         <is>
-          <t>931676</t>
+          <t>931273</t>
         </is>
       </c>
       <c r="T8" s="2" t="inlineStr">
         <is>
-          <t>939451</t>
+          <t>939932</t>
         </is>
       </c>
       <c r="U8" s="2" t="inlineStr">
@@ -2876,12 +2876,12 @@
       </c>
       <c r="V8" s="2" t="inlineStr">
         <is>
-          <t>98,89%</t>
+          <t>98,85%</t>
         </is>
       </c>
       <c r="W8" s="2" t="inlineStr">
         <is>
-          <t>99,72%</t>
+          <t>99,77%</t>
         </is>
       </c>
     </row>
@@ -2894,57 +2894,57 @@
       </c>
       <c r="C9" s="2" t="inlineStr">
         <is>
+          <t>705</t>
+        </is>
+      </c>
+      <c r="D9" s="2" t="inlineStr">
+        <is>
+          <t>492404</t>
+        </is>
+      </c>
+      <c r="E9" s="2" t="inlineStr">
+        <is>
+          <t>492404</t>
+        </is>
+      </c>
+      <c r="F9" s="2" t="inlineStr">
+        <is>
+          <t>492404</t>
+        </is>
+      </c>
+      <c r="G9" s="2" t="inlineStr">
+        <is>
+          <t>100%</t>
+        </is>
+      </c>
+      <c r="H9" s="2" t="inlineStr">
+        <is>
+          <t>100%</t>
+        </is>
+      </c>
+      <c r="I9" s="2" t="inlineStr">
+        <is>
+          <t>100%</t>
+        </is>
+      </c>
+      <c r="J9" s="2" t="inlineStr">
+        <is>
           <t>651</t>
         </is>
       </c>
-      <c r="D9" s="2" t="inlineStr">
+      <c r="K9" s="2" t="inlineStr">
         <is>
           <t>449700</t>
         </is>
       </c>
-      <c r="E9" s="2" t="inlineStr">
+      <c r="L9" s="2" t="inlineStr">
         <is>
           <t>449700</t>
         </is>
       </c>
-      <c r="F9" s="2" t="inlineStr">
+      <c r="M9" s="2" t="inlineStr">
         <is>
           <t>449700</t>
-        </is>
-      </c>
-      <c r="G9" s="2" t="inlineStr">
-        <is>
-          <t>100%</t>
-        </is>
-      </c>
-      <c r="H9" s="2" t="inlineStr">
-        <is>
-          <t>100%</t>
-        </is>
-      </c>
-      <c r="I9" s="2" t="inlineStr">
-        <is>
-          <t>100%</t>
-        </is>
-      </c>
-      <c r="J9" s="2" t="inlineStr">
-        <is>
-          <t>705</t>
-        </is>
-      </c>
-      <c r="K9" s="2" t="inlineStr">
-        <is>
-          <t>492404</t>
-        </is>
-      </c>
-      <c r="L9" s="2" t="inlineStr">
-        <is>
-          <t>492404</t>
-        </is>
-      </c>
-      <c r="M9" s="2" t="inlineStr">
-        <is>
-          <t>492404</t>
         </is>
       </c>
       <c r="N9" s="2" t="inlineStr">
@@ -3011,92 +3011,92 @@
       </c>
       <c r="C10" s="2" t="inlineStr">
         <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="D10" s="2" t="inlineStr">
+        <is>
+          <t>667</t>
+        </is>
+      </c>
+      <c r="E10" s="2" t="inlineStr">
+        <is>
           <t>0</t>
         </is>
       </c>
-      <c r="D10" s="2" t="inlineStr">
+      <c r="F10" s="2" t="inlineStr">
+        <is>
+          <t>3328</t>
+        </is>
+      </c>
+      <c r="G10" s="2" t="inlineStr">
+        <is>
+          <t>0,39%</t>
+        </is>
+      </c>
+      <c r="H10" s="2" t="inlineStr">
+        <is>
+          <t>0,0%</t>
+        </is>
+      </c>
+      <c r="I10" s="2" t="inlineStr">
+        <is>
+          <t>1,94%</t>
+        </is>
+      </c>
+      <c r="J10" s="2" t="inlineStr">
         <is>
           <t>0</t>
         </is>
       </c>
-      <c r="E10" s="2" t="inlineStr">
+      <c r="K10" s="2" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="L10" s="2" t="inlineStr">
         <is>
           <t>—</t>
         </is>
       </c>
-      <c r="F10" s="2" t="inlineStr">
+      <c r="M10" s="2" t="inlineStr">
         <is>
           <t>—</t>
         </is>
       </c>
-      <c r="G10" s="2" t="inlineStr">
+      <c r="N10" s="2" t="inlineStr">
         <is>
           <t>0,0%</t>
         </is>
       </c>
-      <c r="H10" s="2" t="inlineStr">
+      <c r="O10" s="2" t="inlineStr">
         <is>
           <t>—%</t>
         </is>
       </c>
-      <c r="I10" s="2" t="inlineStr">
+      <c r="P10" s="2" t="inlineStr">
         <is>
           <t>—%</t>
         </is>
       </c>
-      <c r="J10" s="2" t="inlineStr">
+      <c r="Q10" s="2" t="inlineStr">
         <is>
           <t>1</t>
         </is>
       </c>
-      <c r="K10" s="2" t="inlineStr">
+      <c r="R10" s="2" t="inlineStr">
         <is>
           <t>667</t>
         </is>
       </c>
-      <c r="L10" s="2" t="inlineStr">
+      <c r="S10" s="2" t="inlineStr">
         <is>
           <t>0</t>
         </is>
       </c>
-      <c r="M10" s="2" t="inlineStr">
-        <is>
-          <t>3865</t>
-        </is>
-      </c>
-      <c r="N10" s="2" t="inlineStr">
-        <is>
-          <t>0,39%</t>
-        </is>
-      </c>
-      <c r="O10" s="2" t="inlineStr">
-        <is>
-          <t>0,0%</t>
-        </is>
-      </c>
-      <c r="P10" s="2" t="inlineStr">
-        <is>
-          <t>2,25%</t>
-        </is>
-      </c>
-      <c r="Q10" s="2" t="inlineStr">
-        <is>
-          <t>1</t>
-        </is>
-      </c>
-      <c r="R10" s="2" t="inlineStr">
-        <is>
-          <t>667</t>
-        </is>
-      </c>
-      <c r="S10" s="2" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
       <c r="T10" s="2" t="inlineStr">
         <is>
-          <t>3362</t>
+          <t>3376</t>
         </is>
       </c>
       <c r="U10" s="2" t="inlineStr">
@@ -3124,74 +3124,74 @@
       </c>
       <c r="C11" s="2" t="inlineStr">
         <is>
+          <t>242</t>
+        </is>
+      </c>
+      <c r="D11" s="2" t="inlineStr">
+        <is>
+          <t>170894</t>
+        </is>
+      </c>
+      <c r="E11" s="2" t="inlineStr">
+        <is>
+          <t>168233</t>
+        </is>
+      </c>
+      <c r="F11" s="2" t="inlineStr">
+        <is>
+          <t>171561</t>
+        </is>
+      </c>
+      <c r="G11" s="2" t="inlineStr">
+        <is>
+          <t>99,61%</t>
+        </is>
+      </c>
+      <c r="H11" s="2" t="inlineStr">
+        <is>
+          <t>98,06%</t>
+        </is>
+      </c>
+      <c r="I11" s="2" t="inlineStr">
+        <is>
+          <t>100,0%</t>
+        </is>
+      </c>
+      <c r="J11" s="2" t="inlineStr">
+        <is>
           <t>234</t>
         </is>
       </c>
-      <c r="D11" s="2" t="inlineStr">
+      <c r="K11" s="2" t="inlineStr">
         <is>
           <t>165340</t>
         </is>
       </c>
-      <c r="E11" s="2" t="inlineStr">
+      <c r="L11" s="2" t="inlineStr">
         <is>
           <t>—</t>
         </is>
       </c>
-      <c r="F11" s="2" t="inlineStr">
+      <c r="M11" s="2" t="inlineStr">
         <is>
           <t>—</t>
         </is>
       </c>
-      <c r="G11" s="2" t="inlineStr">
+      <c r="N11" s="2" t="inlineStr">
         <is>
           <t>100,0%</t>
         </is>
       </c>
-      <c r="H11" s="2" t="inlineStr">
+      <c r="O11" s="2" t="inlineStr">
         <is>
           <t>—%</t>
         </is>
       </c>
-      <c r="I11" s="2" t="inlineStr">
+      <c r="P11" s="2" t="inlineStr">
         <is>
           <t>—%</t>
         </is>
       </c>
-      <c r="J11" s="2" t="inlineStr">
-        <is>
-          <t>242</t>
-        </is>
-      </c>
-      <c r="K11" s="2" t="inlineStr">
-        <is>
-          <t>170894</t>
-        </is>
-      </c>
-      <c r="L11" s="2" t="inlineStr">
-        <is>
-          <t>167696</t>
-        </is>
-      </c>
-      <c r="M11" s="2" t="inlineStr">
-        <is>
-          <t>171561</t>
-        </is>
-      </c>
-      <c r="N11" s="2" t="inlineStr">
-        <is>
-          <t>99,61%</t>
-        </is>
-      </c>
-      <c r="O11" s="2" t="inlineStr">
-        <is>
-          <t>97,75%</t>
-        </is>
-      </c>
-      <c r="P11" s="2" t="inlineStr">
-        <is>
-          <t>100,0%</t>
-        </is>
-      </c>
       <c r="Q11" s="2" t="inlineStr">
         <is>
           <t>476</t>
@@ -3204,7 +3204,7 @@
       </c>
       <c r="S11" s="2" t="inlineStr">
         <is>
-          <t>333539</t>
+          <t>333525</t>
         </is>
       </c>
       <c r="T11" s="2" t="inlineStr">
@@ -3237,57 +3237,57 @@
       </c>
       <c r="C12" s="2" t="inlineStr">
         <is>
+          <t>243</t>
+        </is>
+      </c>
+      <c r="D12" s="2" t="inlineStr">
+        <is>
+          <t>171561</t>
+        </is>
+      </c>
+      <c r="E12" s="2" t="inlineStr">
+        <is>
+          <t>171561</t>
+        </is>
+      </c>
+      <c r="F12" s="2" t="inlineStr">
+        <is>
+          <t>171561</t>
+        </is>
+      </c>
+      <c r="G12" s="2" t="inlineStr">
+        <is>
+          <t>100%</t>
+        </is>
+      </c>
+      <c r="H12" s="2" t="inlineStr">
+        <is>
+          <t>100%</t>
+        </is>
+      </c>
+      <c r="I12" s="2" t="inlineStr">
+        <is>
+          <t>100%</t>
+        </is>
+      </c>
+      <c r="J12" s="2" t="inlineStr">
+        <is>
           <t>234</t>
         </is>
       </c>
-      <c r="D12" s="2" t="inlineStr">
+      <c r="K12" s="2" t="inlineStr">
         <is>
           <t>165340</t>
         </is>
       </c>
-      <c r="E12" s="2" t="inlineStr">
+      <c r="L12" s="2" t="inlineStr">
         <is>
           <t>165340</t>
         </is>
       </c>
-      <c r="F12" s="2" t="inlineStr">
+      <c r="M12" s="2" t="inlineStr">
         <is>
           <t>165340</t>
-        </is>
-      </c>
-      <c r="G12" s="2" t="inlineStr">
-        <is>
-          <t>100%</t>
-        </is>
-      </c>
-      <c r="H12" s="2" t="inlineStr">
-        <is>
-          <t>100%</t>
-        </is>
-      </c>
-      <c r="I12" s="2" t="inlineStr">
-        <is>
-          <t>100%</t>
-        </is>
-      </c>
-      <c r="J12" s="2" t="inlineStr">
-        <is>
-          <t>243</t>
-        </is>
-      </c>
-      <c r="K12" s="2" t="inlineStr">
-        <is>
-          <t>171561</t>
-        </is>
-      </c>
-      <c r="L12" s="2" t="inlineStr">
-        <is>
-          <t>171561</t>
-        </is>
-      </c>
-      <c r="M12" s="2" t="inlineStr">
-        <is>
-          <t>171561</t>
         </is>
       </c>
       <c r="N12" s="2" t="inlineStr">
@@ -3354,74 +3354,74 @@
       </c>
       <c r="C13" s="2" t="inlineStr">
         <is>
+          <t>8</t>
+        </is>
+      </c>
+      <c r="D13" s="2" t="inlineStr">
+        <is>
+          <t>5889</t>
+        </is>
+      </c>
+      <c r="E13" s="2" t="inlineStr">
+        <is>
+          <t>2503</t>
+        </is>
+      </c>
+      <c r="F13" s="2" t="inlineStr">
+        <is>
+          <t>10983</t>
+        </is>
+      </c>
+      <c r="G13" s="2" t="inlineStr">
+        <is>
+          <t>0,79%</t>
+        </is>
+      </c>
+      <c r="H13" s="2" t="inlineStr">
+        <is>
+          <t>0,33%</t>
+        </is>
+      </c>
+      <c r="I13" s="2" t="inlineStr">
+        <is>
+          <t>1,47%</t>
+        </is>
+      </c>
+      <c r="J13" s="2" t="inlineStr">
+        <is>
           <t>2</t>
         </is>
       </c>
-      <c r="D13" s="2" t="inlineStr">
+      <c r="K13" s="2" t="inlineStr">
         <is>
           <t>1346</t>
         </is>
       </c>
-      <c r="E13" s="2" t="inlineStr">
+      <c r="L13" s="2" t="inlineStr">
         <is>
           <t>0</t>
         </is>
       </c>
-      <c r="F13" s="2" t="inlineStr">
-        <is>
-          <t>4709</t>
-        </is>
-      </c>
-      <c r="G13" s="2" t="inlineStr">
+      <c r="M13" s="2" t="inlineStr">
+        <is>
+          <t>4746</t>
+        </is>
+      </c>
+      <c r="N13" s="2" t="inlineStr">
         <is>
           <t>0,19%</t>
         </is>
       </c>
-      <c r="H13" s="2" t="inlineStr">
+      <c r="O13" s="2" t="inlineStr">
         <is>
           <t>0,0%</t>
         </is>
       </c>
-      <c r="I13" s="2" t="inlineStr">
+      <c r="P13" s="2" t="inlineStr">
         <is>
           <t>0,67%</t>
         </is>
       </c>
-      <c r="J13" s="2" t="inlineStr">
-        <is>
-          <t>8</t>
-        </is>
-      </c>
-      <c r="K13" s="2" t="inlineStr">
-        <is>
-          <t>5889</t>
-        </is>
-      </c>
-      <c r="L13" s="2" t="inlineStr">
-        <is>
-          <t>2751</t>
-        </is>
-      </c>
-      <c r="M13" s="2" t="inlineStr">
-        <is>
-          <t>11600</t>
-        </is>
-      </c>
-      <c r="N13" s="2" t="inlineStr">
-        <is>
-          <t>0,79%</t>
-        </is>
-      </c>
-      <c r="O13" s="2" t="inlineStr">
-        <is>
-          <t>0,37%</t>
-        </is>
-      </c>
-      <c r="P13" s="2" t="inlineStr">
-        <is>
-          <t>1,55%</t>
-        </is>
-      </c>
       <c r="Q13" s="2" t="inlineStr">
         <is>
           <t>10</t>
@@ -3434,12 +3434,12 @@
       </c>
       <c r="S13" s="2" t="inlineStr">
         <is>
-          <t>3319</t>
+          <t>3863</t>
         </is>
       </c>
       <c r="T13" s="2" t="inlineStr">
         <is>
-          <t>12384</t>
+          <t>13895</t>
         </is>
       </c>
       <c r="U13" s="2" t="inlineStr">
@@ -3449,12 +3449,12 @@
       </c>
       <c r="V13" s="2" t="inlineStr">
         <is>
-          <t>0,23%</t>
+          <t>0,27%</t>
         </is>
       </c>
       <c r="W13" s="2" t="inlineStr">
         <is>
-          <t>0,85%</t>
+          <t>0,96%</t>
         </is>
       </c>
     </row>
@@ -3467,74 +3467,74 @@
       </c>
       <c r="C14" s="2" t="inlineStr">
         <is>
+          <t>1057</t>
+        </is>
+      </c>
+      <c r="D14" s="2" t="inlineStr">
+        <is>
+          <t>741612</t>
+        </is>
+      </c>
+      <c r="E14" s="2" t="inlineStr">
+        <is>
+          <t>736518</t>
+        </is>
+      </c>
+      <c r="F14" s="2" t="inlineStr">
+        <is>
+          <t>744998</t>
+        </is>
+      </c>
+      <c r="G14" s="2" t="inlineStr">
+        <is>
+          <t>99,21%</t>
+        </is>
+      </c>
+      <c r="H14" s="2" t="inlineStr">
+        <is>
+          <t>98,53%</t>
+        </is>
+      </c>
+      <c r="I14" s="2" t="inlineStr">
+        <is>
+          <t>99,67%</t>
+        </is>
+      </c>
+      <c r="J14" s="2" t="inlineStr">
+        <is>
           <t>1016</t>
         </is>
       </c>
-      <c r="D14" s="2" t="inlineStr">
+      <c r="K14" s="2" t="inlineStr">
         <is>
           <t>705582</t>
         </is>
       </c>
-      <c r="E14" s="2" t="inlineStr">
-        <is>
-          <t>702219</t>
-        </is>
-      </c>
-      <c r="F14" s="2" t="inlineStr">
+      <c r="L14" s="2" t="inlineStr">
+        <is>
+          <t>702182</t>
+        </is>
+      </c>
+      <c r="M14" s="2" t="inlineStr">
         <is>
           <t>706928</t>
         </is>
       </c>
-      <c r="G14" s="2" t="inlineStr">
+      <c r="N14" s="2" t="inlineStr">
         <is>
           <t>99,81%</t>
         </is>
       </c>
-      <c r="H14" s="2" t="inlineStr">
+      <c r="O14" s="2" t="inlineStr">
         <is>
           <t>99,33%</t>
         </is>
       </c>
-      <c r="I14" s="2" t="inlineStr">
+      <c r="P14" s="2" t="inlineStr">
         <is>
           <t>100,0%</t>
         </is>
       </c>
-      <c r="J14" s="2" t="inlineStr">
-        <is>
-          <t>1057</t>
-        </is>
-      </c>
-      <c r="K14" s="2" t="inlineStr">
-        <is>
-          <t>741612</t>
-        </is>
-      </c>
-      <c r="L14" s="2" t="inlineStr">
-        <is>
-          <t>735901</t>
-        </is>
-      </c>
-      <c r="M14" s="2" t="inlineStr">
-        <is>
-          <t>744750</t>
-        </is>
-      </c>
-      <c r="N14" s="2" t="inlineStr">
-        <is>
-          <t>99,21%</t>
-        </is>
-      </c>
-      <c r="O14" s="2" t="inlineStr">
-        <is>
-          <t>98,45%</t>
-        </is>
-      </c>
-      <c r="P14" s="2" t="inlineStr">
-        <is>
-          <t>99,63%</t>
-        </is>
-      </c>
       <c r="Q14" s="2" t="inlineStr">
         <is>
           <t>2073</t>
@@ -3547,12 +3547,12 @@
       </c>
       <c r="S14" s="2" t="inlineStr">
         <is>
-          <t>1442045</t>
+          <t>1440534</t>
         </is>
       </c>
       <c r="T14" s="2" t="inlineStr">
         <is>
-          <t>1451110</t>
+          <t>1450566</t>
         </is>
       </c>
       <c r="U14" s="2" t="inlineStr">
@@ -3562,12 +3562,12 @@
       </c>
       <c r="V14" s="2" t="inlineStr">
         <is>
-          <t>99,15%</t>
+          <t>99,04%</t>
         </is>
       </c>
       <c r="W14" s="2" t="inlineStr">
         <is>
-          <t>99,77%</t>
+          <t>99,73%</t>
         </is>
       </c>
     </row>
@@ -3580,57 +3580,57 @@
       </c>
       <c r="C15" s="2" t="inlineStr">
         <is>
+          <t>1065</t>
+        </is>
+      </c>
+      <c r="D15" s="2" t="inlineStr">
+        <is>
+          <t>747501</t>
+        </is>
+      </c>
+      <c r="E15" s="2" t="inlineStr">
+        <is>
+          <t>747501</t>
+        </is>
+      </c>
+      <c r="F15" s="2" t="inlineStr">
+        <is>
+          <t>747501</t>
+        </is>
+      </c>
+      <c r="G15" s="2" t="inlineStr">
+        <is>
+          <t>100%</t>
+        </is>
+      </c>
+      <c r="H15" s="2" t="inlineStr">
+        <is>
+          <t>100%</t>
+        </is>
+      </c>
+      <c r="I15" s="2" t="inlineStr">
+        <is>
+          <t>100%</t>
+        </is>
+      </c>
+      <c r="J15" s="2" t="inlineStr">
+        <is>
           <t>1018</t>
         </is>
       </c>
-      <c r="D15" s="2" t="inlineStr">
+      <c r="K15" s="2" t="inlineStr">
         <is>
           <t>706928</t>
         </is>
       </c>
-      <c r="E15" s="2" t="inlineStr">
+      <c r="L15" s="2" t="inlineStr">
         <is>
           <t>706928</t>
         </is>
       </c>
-      <c r="F15" s="2" t="inlineStr">
+      <c r="M15" s="2" t="inlineStr">
         <is>
           <t>706928</t>
-        </is>
-      </c>
-      <c r="G15" s="2" t="inlineStr">
-        <is>
-          <t>100%</t>
-        </is>
-      </c>
-      <c r="H15" s="2" t="inlineStr">
-        <is>
-          <t>100%</t>
-        </is>
-      </c>
-      <c r="I15" s="2" t="inlineStr">
-        <is>
-          <t>100%</t>
-        </is>
-      </c>
-      <c r="J15" s="2" t="inlineStr">
-        <is>
-          <t>1065</t>
-        </is>
-      </c>
-      <c r="K15" s="2" t="inlineStr">
-        <is>
-          <t>747501</t>
-        </is>
-      </c>
-      <c r="L15" s="2" t="inlineStr">
-        <is>
-          <t>747501</t>
-        </is>
-      </c>
-      <c r="M15" s="2" t="inlineStr">
-        <is>
-          <t>747501</t>
         </is>
       </c>
       <c r="N15" s="2" t="inlineStr">
@@ -3749,7 +3749,7 @@
       <c r="B1" s="2" t="n"/>
       <c r="C1" s="3" t="inlineStr">
         <is>
-          <t>Niña</t>
+          <t>Niño</t>
         </is>
       </c>
       <c r="D1" s="3" t="n"/>
@@ -3760,7 +3760,7 @@
       <c r="I1" s="3" t="n"/>
       <c r="J1" s="3" t="inlineStr">
         <is>
-          <t>Niño</t>
+          <t>Niña</t>
         </is>
       </c>
       <c r="K1" s="3" t="n"/>
@@ -3928,72 +3928,72 @@
       </c>
       <c r="C4" s="2" t="inlineStr">
         <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="D4" s="2" t="inlineStr">
+        <is>
+          <t>634</t>
+        </is>
+      </c>
+      <c r="E4" s="2" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="F4" s="2" t="inlineStr">
+        <is>
+          <t>3500</t>
+        </is>
+      </c>
+      <c r="G4" s="2" t="inlineStr">
+        <is>
+          <t>0,92%</t>
+        </is>
+      </c>
+      <c r="H4" s="2" t="inlineStr">
+        <is>
+          <t>0,0%</t>
+        </is>
+      </c>
+      <c r="I4" s="2" t="inlineStr">
+        <is>
+          <t>5,1%</t>
+        </is>
+      </c>
+      <c r="J4" s="2" t="inlineStr">
+        <is>
           <t>2</t>
         </is>
       </c>
-      <c r="D4" s="2" t="inlineStr">
+      <c r="K4" s="2" t="inlineStr">
         <is>
           <t>1136</t>
         </is>
       </c>
-      <c r="E4" s="2" t="inlineStr">
+      <c r="L4" s="2" t="inlineStr">
         <is>
           <t>0</t>
         </is>
       </c>
-      <c r="F4" s="2" t="inlineStr">
-        <is>
-          <t>3721</t>
-        </is>
-      </c>
-      <c r="G4" s="2" t="inlineStr">
+      <c r="M4" s="2" t="inlineStr">
+        <is>
+          <t>3826</t>
+        </is>
+      </c>
+      <c r="N4" s="2" t="inlineStr">
         <is>
           <t>1,91%</t>
         </is>
       </c>
-      <c r="H4" s="2" t="inlineStr">
+      <c r="O4" s="2" t="inlineStr">
         <is>
           <t>0,0%</t>
         </is>
       </c>
-      <c r="I4" s="2" t="inlineStr">
-        <is>
-          <t>6,27%</t>
-        </is>
-      </c>
-      <c r="J4" s="2" t="inlineStr">
-        <is>
-          <t>1</t>
-        </is>
-      </c>
-      <c r="K4" s="2" t="inlineStr">
-        <is>
-          <t>634</t>
-        </is>
-      </c>
-      <c r="L4" s="2" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="M4" s="2" t="inlineStr">
-        <is>
-          <t>2623</t>
-        </is>
-      </c>
-      <c r="N4" s="2" t="inlineStr">
-        <is>
-          <t>0,92%</t>
-        </is>
-      </c>
-      <c r="O4" s="2" t="inlineStr">
-        <is>
-          <t>0,0%</t>
-        </is>
-      </c>
       <c r="P4" s="2" t="inlineStr">
         <is>
-          <t>3,82%</t>
+          <t>6,44%</t>
         </is>
       </c>
       <c r="Q4" s="2" t="inlineStr">
@@ -4008,12 +4008,12 @@
       </c>
       <c r="S4" s="2" t="inlineStr">
         <is>
-          <t>529</t>
+          <t>534</t>
         </is>
       </c>
       <c r="T4" s="2" t="inlineStr">
         <is>
-          <t>4777</t>
+          <t>4586</t>
         </is>
       </c>
       <c r="U4" s="2" t="inlineStr">
@@ -4023,12 +4023,12 @@
       </c>
       <c r="V4" s="2" t="inlineStr">
         <is>
-          <t>0,41%</t>
+          <t>0,42%</t>
         </is>
       </c>
       <c r="W4" s="2" t="inlineStr">
         <is>
-          <t>3,73%</t>
+          <t>3,58%</t>
         </is>
       </c>
     </row>
@@ -4041,74 +4041,74 @@
       </c>
       <c r="C5" s="2" t="inlineStr">
         <is>
+          <t>98</t>
+        </is>
+      </c>
+      <c r="D5" s="2" t="inlineStr">
+        <is>
+          <t>67980</t>
+        </is>
+      </c>
+      <c r="E5" s="2" t="inlineStr">
+        <is>
+          <t>65114</t>
+        </is>
+      </c>
+      <c r="F5" s="2" t="inlineStr">
+        <is>
+          <t>68614</t>
+        </is>
+      </c>
+      <c r="G5" s="2" t="inlineStr">
+        <is>
+          <t>99,08%</t>
+        </is>
+      </c>
+      <c r="H5" s="2" t="inlineStr">
+        <is>
+          <t>94,9%</t>
+        </is>
+      </c>
+      <c r="I5" s="2" t="inlineStr">
+        <is>
+          <t>100,0%</t>
+        </is>
+      </c>
+      <c r="J5" s="2" t="inlineStr">
+        <is>
           <t>87</t>
         </is>
       </c>
-      <c r="D5" s="2" t="inlineStr">
+      <c r="K5" s="2" t="inlineStr">
         <is>
           <t>58242</t>
         </is>
       </c>
-      <c r="E5" s="2" t="inlineStr">
-        <is>
-          <t>55657</t>
-        </is>
-      </c>
-      <c r="F5" s="2" t="inlineStr">
+      <c r="L5" s="2" t="inlineStr">
+        <is>
+          <t>55552</t>
+        </is>
+      </c>
+      <c r="M5" s="2" t="inlineStr">
         <is>
           <t>59378</t>
         </is>
       </c>
-      <c r="G5" s="2" t="inlineStr">
+      <c r="N5" s="2" t="inlineStr">
         <is>
           <t>98,09%</t>
         </is>
       </c>
-      <c r="H5" s="2" t="inlineStr">
-        <is>
-          <t>93,73%</t>
-        </is>
-      </c>
-      <c r="I5" s="2" t="inlineStr">
+      <c r="O5" s="2" t="inlineStr">
+        <is>
+          <t>93,56%</t>
+        </is>
+      </c>
+      <c r="P5" s="2" t="inlineStr">
         <is>
           <t>100,0%</t>
         </is>
       </c>
-      <c r="J5" s="2" t="inlineStr">
-        <is>
-          <t>98</t>
-        </is>
-      </c>
-      <c r="K5" s="2" t="inlineStr">
-        <is>
-          <t>67980</t>
-        </is>
-      </c>
-      <c r="L5" s="2" t="inlineStr">
-        <is>
-          <t>65991</t>
-        </is>
-      </c>
-      <c r="M5" s="2" t="inlineStr">
-        <is>
-          <t>68614</t>
-        </is>
-      </c>
-      <c r="N5" s="2" t="inlineStr">
-        <is>
-          <t>99,08%</t>
-        </is>
-      </c>
-      <c r="O5" s="2" t="inlineStr">
-        <is>
-          <t>96,18%</t>
-        </is>
-      </c>
-      <c r="P5" s="2" t="inlineStr">
-        <is>
-          <t>100,0%</t>
-        </is>
-      </c>
       <c r="Q5" s="2" t="inlineStr">
         <is>
           <t>185</t>
@@ -4121,12 +4121,12 @@
       </c>
       <c r="S5" s="2" t="inlineStr">
         <is>
-          <t>123216</t>
+          <t>123407</t>
         </is>
       </c>
       <c r="T5" s="2" t="inlineStr">
         <is>
-          <t>127464</t>
+          <t>127459</t>
         </is>
       </c>
       <c r="U5" s="2" t="inlineStr">
@@ -4136,12 +4136,12 @@
       </c>
       <c r="V5" s="2" t="inlineStr">
         <is>
-          <t>96,27%</t>
+          <t>96,42%</t>
         </is>
       </c>
       <c r="W5" s="2" t="inlineStr">
         <is>
-          <t>99,59%</t>
+          <t>99,58%</t>
         </is>
       </c>
     </row>
@@ -4154,57 +4154,57 @@
       </c>
       <c r="C6" s="2" t="inlineStr">
         <is>
+          <t>99</t>
+        </is>
+      </c>
+      <c r="D6" s="2" t="inlineStr">
+        <is>
+          <t>68614</t>
+        </is>
+      </c>
+      <c r="E6" s="2" t="inlineStr">
+        <is>
+          <t>68614</t>
+        </is>
+      </c>
+      <c r="F6" s="2" t="inlineStr">
+        <is>
+          <t>68614</t>
+        </is>
+      </c>
+      <c r="G6" s="2" t="inlineStr">
+        <is>
+          <t>100%</t>
+        </is>
+      </c>
+      <c r="H6" s="2" t="inlineStr">
+        <is>
+          <t>100%</t>
+        </is>
+      </c>
+      <c r="I6" s="2" t="inlineStr">
+        <is>
+          <t>100%</t>
+        </is>
+      </c>
+      <c r="J6" s="2" t="inlineStr">
+        <is>
           <t>89</t>
         </is>
       </c>
-      <c r="D6" s="2" t="inlineStr">
+      <c r="K6" s="2" t="inlineStr">
         <is>
           <t>59378</t>
         </is>
       </c>
-      <c r="E6" s="2" t="inlineStr">
+      <c r="L6" s="2" t="inlineStr">
         <is>
           <t>59378</t>
         </is>
       </c>
-      <c r="F6" s="2" t="inlineStr">
+      <c r="M6" s="2" t="inlineStr">
         <is>
           <t>59378</t>
-        </is>
-      </c>
-      <c r="G6" s="2" t="inlineStr">
-        <is>
-          <t>100%</t>
-        </is>
-      </c>
-      <c r="H6" s="2" t="inlineStr">
-        <is>
-          <t>100%</t>
-        </is>
-      </c>
-      <c r="I6" s="2" t="inlineStr">
-        <is>
-          <t>100%</t>
-        </is>
-      </c>
-      <c r="J6" s="2" t="inlineStr">
-        <is>
-          <t>99</t>
-        </is>
-      </c>
-      <c r="K6" s="2" t="inlineStr">
-        <is>
-          <t>68614</t>
-        </is>
-      </c>
-      <c r="L6" s="2" t="inlineStr">
-        <is>
-          <t>68614</t>
-        </is>
-      </c>
-      <c r="M6" s="2" t="inlineStr">
-        <is>
-          <t>68614</t>
         </is>
       </c>
       <c r="N6" s="2" t="inlineStr">
@@ -4276,67 +4276,67 @@
       </c>
       <c r="D7" s="2" t="inlineStr">
         <is>
+          <t>1366</t>
+        </is>
+      </c>
+      <c r="E7" s="2" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="F7" s="2" t="inlineStr">
+        <is>
+          <t>4301</t>
+        </is>
+      </c>
+      <c r="G7" s="2" t="inlineStr">
+        <is>
+          <t>0,28%</t>
+        </is>
+      </c>
+      <c r="H7" s="2" t="inlineStr">
+        <is>
+          <t>0,0%</t>
+        </is>
+      </c>
+      <c r="I7" s="2" t="inlineStr">
+        <is>
+          <t>0,88%</t>
+        </is>
+      </c>
+      <c r="J7" s="2" t="inlineStr">
+        <is>
+          <t>2</t>
+        </is>
+      </c>
+      <c r="K7" s="2" t="inlineStr">
+        <is>
           <t>1537</t>
         </is>
       </c>
-      <c r="E7" s="2" t="inlineStr">
+      <c r="L7" s="2" t="inlineStr">
         <is>
           <t>0</t>
         </is>
       </c>
-      <c r="F7" s="2" t="inlineStr">
-        <is>
-          <t>5018</t>
-        </is>
-      </c>
-      <c r="G7" s="2" t="inlineStr">
+      <c r="M7" s="2" t="inlineStr">
+        <is>
+          <t>5269</t>
+        </is>
+      </c>
+      <c r="N7" s="2" t="inlineStr">
         <is>
           <t>0,33%</t>
         </is>
       </c>
-      <c r="H7" s="2" t="inlineStr">
+      <c r="O7" s="2" t="inlineStr">
         <is>
           <t>0,0%</t>
         </is>
       </c>
-      <c r="I7" s="2" t="inlineStr">
-        <is>
-          <t>1,06%</t>
-        </is>
-      </c>
-      <c r="J7" s="2" t="inlineStr">
-        <is>
-          <t>2</t>
-        </is>
-      </c>
-      <c r="K7" s="2" t="inlineStr">
-        <is>
-          <t>1366</t>
-        </is>
-      </c>
-      <c r="L7" s="2" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="M7" s="2" t="inlineStr">
-        <is>
-          <t>4328</t>
-        </is>
-      </c>
-      <c r="N7" s="2" t="inlineStr">
-        <is>
-          <t>0,28%</t>
-        </is>
-      </c>
-      <c r="O7" s="2" t="inlineStr">
-        <is>
-          <t>0,0%</t>
-        </is>
-      </c>
       <c r="P7" s="2" t="inlineStr">
         <is>
-          <t>0,89%</t>
+          <t>1,12%</t>
         </is>
       </c>
       <c r="Q7" s="2" t="inlineStr">
@@ -4351,12 +4351,12 @@
       </c>
       <c r="S7" s="2" t="inlineStr">
         <is>
-          <t>665</t>
+          <t>870</t>
         </is>
       </c>
       <c r="T7" s="2" t="inlineStr">
         <is>
-          <t>6827</t>
+          <t>8115</t>
         </is>
       </c>
       <c r="U7" s="2" t="inlineStr">
@@ -4366,12 +4366,12 @@
       </c>
       <c r="V7" s="2" t="inlineStr">
         <is>
-          <t>0,07%</t>
+          <t>0,09%</t>
         </is>
       </c>
       <c r="W7" s="2" t="inlineStr">
         <is>
-          <t>0,71%</t>
+          <t>0,84%</t>
         </is>
       </c>
     </row>
@@ -4384,74 +4384,74 @@
       </c>
       <c r="C8" s="2" t="inlineStr">
         <is>
+          <t>693</t>
+        </is>
+      </c>
+      <c r="D8" s="2" t="inlineStr">
+        <is>
+          <t>487369</t>
+        </is>
+      </c>
+      <c r="E8" s="2" t="inlineStr">
+        <is>
+          <t>484434</t>
+        </is>
+      </c>
+      <c r="F8" s="2" t="inlineStr">
+        <is>
+          <t>488735</t>
+        </is>
+      </c>
+      <c r="G8" s="2" t="inlineStr">
+        <is>
+          <t>99,72%</t>
+        </is>
+      </c>
+      <c r="H8" s="2" t="inlineStr">
+        <is>
+          <t>99,12%</t>
+        </is>
+      </c>
+      <c r="I8" s="2" t="inlineStr">
+        <is>
+          <t>100,0%</t>
+        </is>
+      </c>
+      <c r="J8" s="2" t="inlineStr">
+        <is>
           <t>712</t>
         </is>
       </c>
-      <c r="D8" s="2" t="inlineStr">
+      <c r="K8" s="2" t="inlineStr">
         <is>
           <t>470753</t>
         </is>
       </c>
-      <c r="E8" s="2" t="inlineStr">
-        <is>
-          <t>467272</t>
-        </is>
-      </c>
-      <c r="F8" s="2" t="inlineStr">
+      <c r="L8" s="2" t="inlineStr">
+        <is>
+          <t>467021</t>
+        </is>
+      </c>
+      <c r="M8" s="2" t="inlineStr">
         <is>
           <t>472290</t>
         </is>
       </c>
-      <c r="G8" s="2" t="inlineStr">
+      <c r="N8" s="2" t="inlineStr">
         <is>
           <t>99,67%</t>
         </is>
       </c>
-      <c r="H8" s="2" t="inlineStr">
-        <is>
-          <t>98,94%</t>
-        </is>
-      </c>
-      <c r="I8" s="2" t="inlineStr">
+      <c r="O8" s="2" t="inlineStr">
+        <is>
+          <t>98,88%</t>
+        </is>
+      </c>
+      <c r="P8" s="2" t="inlineStr">
         <is>
           <t>100,0%</t>
         </is>
       </c>
-      <c r="J8" s="2" t="inlineStr">
-        <is>
-          <t>693</t>
-        </is>
-      </c>
-      <c r="K8" s="2" t="inlineStr">
-        <is>
-          <t>487369</t>
-        </is>
-      </c>
-      <c r="L8" s="2" t="inlineStr">
-        <is>
-          <t>484407</t>
-        </is>
-      </c>
-      <c r="M8" s="2" t="inlineStr">
-        <is>
-          <t>488735</t>
-        </is>
-      </c>
-      <c r="N8" s="2" t="inlineStr">
-        <is>
-          <t>99,72%</t>
-        </is>
-      </c>
-      <c r="O8" s="2" t="inlineStr">
-        <is>
-          <t>99,11%</t>
-        </is>
-      </c>
-      <c r="P8" s="2" t="inlineStr">
-        <is>
-          <t>100,0%</t>
-        </is>
-      </c>
       <c r="Q8" s="2" t="inlineStr">
         <is>
           <t>1405</t>
@@ -4464,12 +4464,12 @@
       </c>
       <c r="S8" s="2" t="inlineStr">
         <is>
-          <t>954198</t>
+          <t>952910</t>
         </is>
       </c>
       <c r="T8" s="2" t="inlineStr">
         <is>
-          <t>960360</t>
+          <t>960155</t>
         </is>
       </c>
       <c r="U8" s="2" t="inlineStr">
@@ -4479,12 +4479,12 @@
       </c>
       <c r="V8" s="2" t="inlineStr">
         <is>
-          <t>99,29%</t>
+          <t>99,16%</t>
         </is>
       </c>
       <c r="W8" s="2" t="inlineStr">
         <is>
-          <t>99,93%</t>
+          <t>99,91%</t>
         </is>
       </c>
     </row>
@@ -4497,57 +4497,57 @@
       </c>
       <c r="C9" s="2" t="inlineStr">
         <is>
+          <t>695</t>
+        </is>
+      </c>
+      <c r="D9" s="2" t="inlineStr">
+        <is>
+          <t>488735</t>
+        </is>
+      </c>
+      <c r="E9" s="2" t="inlineStr">
+        <is>
+          <t>488735</t>
+        </is>
+      </c>
+      <c r="F9" s="2" t="inlineStr">
+        <is>
+          <t>488735</t>
+        </is>
+      </c>
+      <c r="G9" s="2" t="inlineStr">
+        <is>
+          <t>100%</t>
+        </is>
+      </c>
+      <c r="H9" s="2" t="inlineStr">
+        <is>
+          <t>100%</t>
+        </is>
+      </c>
+      <c r="I9" s="2" t="inlineStr">
+        <is>
+          <t>100%</t>
+        </is>
+      </c>
+      <c r="J9" s="2" t="inlineStr">
+        <is>
           <t>714</t>
         </is>
       </c>
-      <c r="D9" s="2" t="inlineStr">
+      <c r="K9" s="2" t="inlineStr">
         <is>
           <t>472290</t>
         </is>
       </c>
-      <c r="E9" s="2" t="inlineStr">
+      <c r="L9" s="2" t="inlineStr">
         <is>
           <t>472290</t>
         </is>
       </c>
-      <c r="F9" s="2" t="inlineStr">
+      <c r="M9" s="2" t="inlineStr">
         <is>
           <t>472290</t>
-        </is>
-      </c>
-      <c r="G9" s="2" t="inlineStr">
-        <is>
-          <t>100%</t>
-        </is>
-      </c>
-      <c r="H9" s="2" t="inlineStr">
-        <is>
-          <t>100%</t>
-        </is>
-      </c>
-      <c r="I9" s="2" t="inlineStr">
-        <is>
-          <t>100%</t>
-        </is>
-      </c>
-      <c r="J9" s="2" t="inlineStr">
-        <is>
-          <t>695</t>
-        </is>
-      </c>
-      <c r="K9" s="2" t="inlineStr">
-        <is>
-          <t>488735</t>
-        </is>
-      </c>
-      <c r="L9" s="2" t="inlineStr">
-        <is>
-          <t>488735</t>
-        </is>
-      </c>
-      <c r="M9" s="2" t="inlineStr">
-        <is>
-          <t>488735</t>
         </is>
       </c>
       <c r="N9" s="2" t="inlineStr">
@@ -4727,47 +4727,47 @@
       </c>
       <c r="C11" s="2" t="inlineStr">
         <is>
+          <t>271</t>
+        </is>
+      </c>
+      <c r="D11" s="2" t="inlineStr">
+        <is>
+          <t>187495</t>
+        </is>
+      </c>
+      <c r="E11" s="2" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="F11" s="2" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="G11" s="2" t="inlineStr">
+        <is>
+          <t>100,0%</t>
+        </is>
+      </c>
+      <c r="H11" s="2" t="inlineStr">
+        <is>
+          <t>—%</t>
+        </is>
+      </c>
+      <c r="I11" s="2" t="inlineStr">
+        <is>
+          <t>—%</t>
+        </is>
+      </c>
+      <c r="J11" s="2" t="inlineStr">
+        <is>
           <t>258</t>
         </is>
       </c>
-      <c r="D11" s="2" t="inlineStr">
+      <c r="K11" s="2" t="inlineStr">
         <is>
           <t>172703</t>
-        </is>
-      </c>
-      <c r="E11" s="2" t="inlineStr">
-        <is>
-          <t>—</t>
-        </is>
-      </c>
-      <c r="F11" s="2" t="inlineStr">
-        <is>
-          <t>—</t>
-        </is>
-      </c>
-      <c r="G11" s="2" t="inlineStr">
-        <is>
-          <t>100,0%</t>
-        </is>
-      </c>
-      <c r="H11" s="2" t="inlineStr">
-        <is>
-          <t>—%</t>
-        </is>
-      </c>
-      <c r="I11" s="2" t="inlineStr">
-        <is>
-          <t>—%</t>
-        </is>
-      </c>
-      <c r="J11" s="2" t="inlineStr">
-        <is>
-          <t>271</t>
-        </is>
-      </c>
-      <c r="K11" s="2" t="inlineStr">
-        <is>
-          <t>187495</t>
         </is>
       </c>
       <c r="L11" s="2" t="inlineStr">
@@ -4840,57 +4840,57 @@
       </c>
       <c r="C12" s="2" t="inlineStr">
         <is>
+          <t>271</t>
+        </is>
+      </c>
+      <c r="D12" s="2" t="inlineStr">
+        <is>
+          <t>187495</t>
+        </is>
+      </c>
+      <c r="E12" s="2" t="inlineStr">
+        <is>
+          <t>187495</t>
+        </is>
+      </c>
+      <c r="F12" s="2" t="inlineStr">
+        <is>
+          <t>187495</t>
+        </is>
+      </c>
+      <c r="G12" s="2" t="inlineStr">
+        <is>
+          <t>100%</t>
+        </is>
+      </c>
+      <c r="H12" s="2" t="inlineStr">
+        <is>
+          <t>100%</t>
+        </is>
+      </c>
+      <c r="I12" s="2" t="inlineStr">
+        <is>
+          <t>100%</t>
+        </is>
+      </c>
+      <c r="J12" s="2" t="inlineStr">
+        <is>
           <t>258</t>
         </is>
       </c>
-      <c r="D12" s="2" t="inlineStr">
+      <c r="K12" s="2" t="inlineStr">
         <is>
           <t>172703</t>
         </is>
       </c>
-      <c r="E12" s="2" t="inlineStr">
+      <c r="L12" s="2" t="inlineStr">
         <is>
           <t>172703</t>
         </is>
       </c>
-      <c r="F12" s="2" t="inlineStr">
+      <c r="M12" s="2" t="inlineStr">
         <is>
           <t>172703</t>
-        </is>
-      </c>
-      <c r="G12" s="2" t="inlineStr">
-        <is>
-          <t>100%</t>
-        </is>
-      </c>
-      <c r="H12" s="2" t="inlineStr">
-        <is>
-          <t>100%</t>
-        </is>
-      </c>
-      <c r="I12" s="2" t="inlineStr">
-        <is>
-          <t>100%</t>
-        </is>
-      </c>
-      <c r="J12" s="2" t="inlineStr">
-        <is>
-          <t>271</t>
-        </is>
-      </c>
-      <c r="K12" s="2" t="inlineStr">
-        <is>
-          <t>187495</t>
-        </is>
-      </c>
-      <c r="L12" s="2" t="inlineStr">
-        <is>
-          <t>187495</t>
-        </is>
-      </c>
-      <c r="M12" s="2" t="inlineStr">
-        <is>
-          <t>187495</t>
         </is>
       </c>
       <c r="N12" s="2" t="inlineStr">
@@ -4957,72 +4957,72 @@
       </c>
       <c r="C13" s="2" t="inlineStr">
         <is>
+          <t>3</t>
+        </is>
+      </c>
+      <c r="D13" s="2" t="inlineStr">
+        <is>
+          <t>1999</t>
+        </is>
+      </c>
+      <c r="E13" s="2" t="inlineStr">
+        <is>
+          <t>627</t>
+        </is>
+      </c>
+      <c r="F13" s="2" t="inlineStr">
+        <is>
+          <t>6071</t>
+        </is>
+      </c>
+      <c r="G13" s="2" t="inlineStr">
+        <is>
+          <t>0,27%</t>
+        </is>
+      </c>
+      <c r="H13" s="2" t="inlineStr">
+        <is>
+          <t>0,08%</t>
+        </is>
+      </c>
+      <c r="I13" s="2" t="inlineStr">
+        <is>
+          <t>0,82%</t>
+        </is>
+      </c>
+      <c r="J13" s="2" t="inlineStr">
+        <is>
           <t>4</t>
         </is>
       </c>
-      <c r="D13" s="2" t="inlineStr">
+      <c r="K13" s="2" t="inlineStr">
         <is>
           <t>2673</t>
         </is>
       </c>
-      <c r="E13" s="2" t="inlineStr">
-        <is>
-          <t>658</t>
-        </is>
-      </c>
-      <c r="F13" s="2" t="inlineStr">
-        <is>
-          <t>6757</t>
-        </is>
-      </c>
-      <c r="G13" s="2" t="inlineStr">
+      <c r="L13" s="2" t="inlineStr">
+        <is>
+          <t>602</t>
+        </is>
+      </c>
+      <c r="M13" s="2" t="inlineStr">
+        <is>
+          <t>6913</t>
+        </is>
+      </c>
+      <c r="N13" s="2" t="inlineStr">
         <is>
           <t>0,38%</t>
         </is>
       </c>
-      <c r="H13" s="2" t="inlineStr">
+      <c r="O13" s="2" t="inlineStr">
         <is>
           <t>0,09%</t>
         </is>
       </c>
-      <c r="I13" s="2" t="inlineStr">
-        <is>
-          <t>0,96%</t>
-        </is>
-      </c>
-      <c r="J13" s="2" t="inlineStr">
-        <is>
-          <t>3</t>
-        </is>
-      </c>
-      <c r="K13" s="2" t="inlineStr">
-        <is>
-          <t>1999</t>
-        </is>
-      </c>
-      <c r="L13" s="2" t="inlineStr">
-        <is>
-          <t>626</t>
-        </is>
-      </c>
-      <c r="M13" s="2" t="inlineStr">
-        <is>
-          <t>5491</t>
-        </is>
-      </c>
-      <c r="N13" s="2" t="inlineStr">
-        <is>
-          <t>0,27%</t>
-        </is>
-      </c>
-      <c r="O13" s="2" t="inlineStr">
-        <is>
-          <t>0,08%</t>
-        </is>
-      </c>
       <c r="P13" s="2" t="inlineStr">
         <is>
-          <t>0,74%</t>
+          <t>0,98%</t>
         </is>
       </c>
       <c r="Q13" s="2" t="inlineStr">
@@ -5037,12 +5037,12 @@
       </c>
       <c r="S13" s="2" t="inlineStr">
         <is>
-          <t>2001</t>
+          <t>1880</t>
         </is>
       </c>
       <c r="T13" s="2" t="inlineStr">
         <is>
-          <t>9605</t>
+          <t>9152</t>
         </is>
       </c>
       <c r="U13" s="2" t="inlineStr">
@@ -5052,12 +5052,12 @@
       </c>
       <c r="V13" s="2" t="inlineStr">
         <is>
-          <t>0,14%</t>
+          <t>0,13%</t>
         </is>
       </c>
       <c r="W13" s="2" t="inlineStr">
         <is>
-          <t>0,66%</t>
+          <t>0,63%</t>
         </is>
       </c>
     </row>
@@ -5070,74 +5070,74 @@
       </c>
       <c r="C14" s="2" t="inlineStr">
         <is>
+          <t>1062</t>
+        </is>
+      </c>
+      <c r="D14" s="2" t="inlineStr">
+        <is>
+          <t>742845</t>
+        </is>
+      </c>
+      <c r="E14" s="2" t="inlineStr">
+        <is>
+          <t>738773</t>
+        </is>
+      </c>
+      <c r="F14" s="2" t="inlineStr">
+        <is>
+          <t>744217</t>
+        </is>
+      </c>
+      <c r="G14" s="2" t="inlineStr">
+        <is>
+          <t>99,73%</t>
+        </is>
+      </c>
+      <c r="H14" s="2" t="inlineStr">
+        <is>
+          <t>99,18%</t>
+        </is>
+      </c>
+      <c r="I14" s="2" t="inlineStr">
+        <is>
+          <t>99,92%</t>
+        </is>
+      </c>
+      <c r="J14" s="2" t="inlineStr">
+        <is>
           <t>1057</t>
         </is>
       </c>
-      <c r="D14" s="2" t="inlineStr">
+      <c r="K14" s="2" t="inlineStr">
         <is>
           <t>701698</t>
         </is>
       </c>
-      <c r="E14" s="2" t="inlineStr">
-        <is>
-          <t>697614</t>
-        </is>
-      </c>
-      <c r="F14" s="2" t="inlineStr">
-        <is>
-          <t>703713</t>
-        </is>
-      </c>
-      <c r="G14" s="2" t="inlineStr">
+      <c r="L14" s="2" t="inlineStr">
+        <is>
+          <t>697458</t>
+        </is>
+      </c>
+      <c r="M14" s="2" t="inlineStr">
+        <is>
+          <t>703769</t>
+        </is>
+      </c>
+      <c r="N14" s="2" t="inlineStr">
         <is>
           <t>99,62%</t>
         </is>
       </c>
-      <c r="H14" s="2" t="inlineStr">
-        <is>
-          <t>99,04%</t>
-        </is>
-      </c>
-      <c r="I14" s="2" t="inlineStr">
+      <c r="O14" s="2" t="inlineStr">
+        <is>
+          <t>99,02%</t>
+        </is>
+      </c>
+      <c r="P14" s="2" t="inlineStr">
         <is>
           <t>99,91%</t>
         </is>
       </c>
-      <c r="J14" s="2" t="inlineStr">
-        <is>
-          <t>1062</t>
-        </is>
-      </c>
-      <c r="K14" s="2" t="inlineStr">
-        <is>
-          <t>742845</t>
-        </is>
-      </c>
-      <c r="L14" s="2" t="inlineStr">
-        <is>
-          <t>739353</t>
-        </is>
-      </c>
-      <c r="M14" s="2" t="inlineStr">
-        <is>
-          <t>744218</t>
-        </is>
-      </c>
-      <c r="N14" s="2" t="inlineStr">
-        <is>
-          <t>99,73%</t>
-        </is>
-      </c>
-      <c r="O14" s="2" t="inlineStr">
-        <is>
-          <t>99,26%</t>
-        </is>
-      </c>
-      <c r="P14" s="2" t="inlineStr">
-        <is>
-          <t>99,92%</t>
-        </is>
-      </c>
       <c r="Q14" s="2" t="inlineStr">
         <is>
           <t>2119</t>
@@ -5150,12 +5150,12 @@
       </c>
       <c r="S14" s="2" t="inlineStr">
         <is>
-          <t>1439610</t>
+          <t>1440063</t>
         </is>
       </c>
       <c r="T14" s="2" t="inlineStr">
         <is>
-          <t>1447214</t>
+          <t>1447335</t>
         </is>
       </c>
       <c r="U14" s="2" t="inlineStr">
@@ -5165,12 +5165,12 @@
       </c>
       <c r="V14" s="2" t="inlineStr">
         <is>
-          <t>99,34%</t>
+          <t>99,37%</t>
         </is>
       </c>
       <c r="W14" s="2" t="inlineStr">
         <is>
-          <t>99,86%</t>
+          <t>99,87%</t>
         </is>
       </c>
     </row>
@@ -5183,57 +5183,57 @@
       </c>
       <c r="C15" s="2" t="inlineStr">
         <is>
+          <t>1065</t>
+        </is>
+      </c>
+      <c r="D15" s="2" t="inlineStr">
+        <is>
+          <t>744844</t>
+        </is>
+      </c>
+      <c r="E15" s="2" t="inlineStr">
+        <is>
+          <t>744844</t>
+        </is>
+      </c>
+      <c r="F15" s="2" t="inlineStr">
+        <is>
+          <t>744844</t>
+        </is>
+      </c>
+      <c r="G15" s="2" t="inlineStr">
+        <is>
+          <t>100%</t>
+        </is>
+      </c>
+      <c r="H15" s="2" t="inlineStr">
+        <is>
+          <t>100%</t>
+        </is>
+      </c>
+      <c r="I15" s="2" t="inlineStr">
+        <is>
+          <t>100%</t>
+        </is>
+      </c>
+      <c r="J15" s="2" t="inlineStr">
+        <is>
           <t>1061</t>
         </is>
       </c>
-      <c r="D15" s="2" t="inlineStr">
+      <c r="K15" s="2" t="inlineStr">
         <is>
           <t>704371</t>
         </is>
       </c>
-      <c r="E15" s="2" t="inlineStr">
+      <c r="L15" s="2" t="inlineStr">
         <is>
           <t>704371</t>
         </is>
       </c>
-      <c r="F15" s="2" t="inlineStr">
+      <c r="M15" s="2" t="inlineStr">
         <is>
           <t>704371</t>
-        </is>
-      </c>
-      <c r="G15" s="2" t="inlineStr">
-        <is>
-          <t>100%</t>
-        </is>
-      </c>
-      <c r="H15" s="2" t="inlineStr">
-        <is>
-          <t>100%</t>
-        </is>
-      </c>
-      <c r="I15" s="2" t="inlineStr">
-        <is>
-          <t>100%</t>
-        </is>
-      </c>
-      <c r="J15" s="2" t="inlineStr">
-        <is>
-          <t>1065</t>
-        </is>
-      </c>
-      <c r="K15" s="2" t="inlineStr">
-        <is>
-          <t>744844</t>
-        </is>
-      </c>
-      <c r="L15" s="2" t="inlineStr">
-        <is>
-          <t>744844</t>
-        </is>
-      </c>
-      <c r="M15" s="2" t="inlineStr">
-        <is>
-          <t>744844</t>
         </is>
       </c>
       <c r="N15" s="2" t="inlineStr">
